--- a/data/merged/2026-08-31/MERGED_IT_Spot-Cleaner_2026-08-31.xlsx
+++ b/data/merged/2026-08-31/MERGED_IT_Spot-Cleaner_2026-08-31.xlsx
@@ -6256,13 +6256,13 @@
       <xdr:col>1</xdr:col>
       <xdr:colOff>192000</xdr:colOff>
       <xdr:row>33</xdr:row>
-      <xdr:rowOff>45000</xdr:rowOff>
+      <xdr:rowOff>44999</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>1</xdr:col>
       <xdr:colOff>428799</xdr:colOff>
       <xdr:row>33</xdr:row>
-      <xdr:rowOff>270000</xdr:rowOff>
+      <xdr:rowOff>269999</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -6955,94 +6955,6 @@
     </xdr:pic>
     <xdr:clientData/>
   </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>192000</xdr:colOff>
-      <xdr:row>49</xdr:row>
-      <xdr:rowOff>44999</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>428799</xdr:colOff>
-      <xdr:row>49</xdr:row>
-      <xdr:rowOff>269999</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="49" name="Product 49">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <ns2:creationId id="{00000000-0008-0000-0000-000002000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip r:embed="rId49" cstate="print"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="0" cy="0"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>192000</xdr:colOff>
-      <xdr:row>50</xdr:row>
-      <xdr:rowOff>44999</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>428799</xdr:colOff>
-      <xdr:row>50</xdr:row>
-      <xdr:rowOff>269999</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="50" name="Product 50">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <ns2:creationId id="{00000000-0008-0000-0000-000002000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip r:embed="rId50" cstate="print"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="0" cy="0"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
 </xdr:wsDr>
 </file>
 
@@ -7368,7 +7280,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:BR51"/>
+  <dimension ref="A1:BR49"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="5" style="1" customWidth="1"/>
@@ -14951,129 +14863,125 @@
       <c r="B34" s="13"/>
       <c r="C34" s="14" t="inlineStr">
         <is>
-          <t>B0753NXDPR</t>
+          <t>B0H3LCDNGF</t>
         </is>
       </c>
       <c r="D34" s="14"/>
       <c r="E34" s="14"/>
       <c r="F34" s="14" t="inlineStr">
         <is>
-          <t>Bissell</t>
+          <t>LEHMANN POLSKA</t>
         </is>
       </c>
       <c r="G34" s="14" t="inlineStr">
         <is>
-          <t>https://www.amazon.it/stores/BISSELL/page/EDA95B6C-7064-466B-BACA-347C73A9A423?lp_asin=B0753NXDPR&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto</t>
+          <t>https://www.amazon.it/stores/LEHMANN/page/F8312757-EA08-4E70-8102-256521882264?lp_asin=B0H3LCDNGF&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto&amp;bl_grd_status=override</t>
         </is>
       </c>
       <c r="H34" s="14" t="inlineStr">
         <is>
-          <t>BISSELL Oxygen Boost Potenziatore Detergente 1 L 1134NsPer formule detergenti per pulitori portatili SpotClean, per moquett</t>
+          <t>LEHMANN SteamWash 1800 Lavatappezzeria e Pulitore a Vapore 4 in 1, Lavatappeti e Divani con Acqua Calda 60°C e Vapore 116°C,</t>
         </is>
       </c>
       <c r="I34" s="14"/>
       <c r="J34" s="14" t="inlineStr">
         <is>
-          <t>https://www.amazon.it/dp/B0753NXDPR?psc=1</t>
+          <t>https://www.amazon.it/dp/B0H3LCDNGF?psc=1</t>
         </is>
       </c>
       <c r="K34" s="14" t="inlineStr">
         <is>
-          <t>https://m.media-amazon.com/images/I/31BhvLWbbNL._AC_US600_.jpg</t>
+          <t>https://m.media-amazon.com/images/I/41Md9nniqDL._AC_US600_.jpg</t>
         </is>
       </c>
       <c r="L34" s="14" t="inlineStr">
         <is>
-          <t>B0753NXDPR</t>
+          <t>B0H3LCDNGF</t>
         </is>
       </c>
       <c r="M34" s="14" t="inlineStr">
         <is>
-          <t>Salute e cura della persona:Pulizia e cura della casa:Detergenti per la casa:Detergenti per tappeti:Detersivi lavaggio a macchina tappeti</t>
+          <t>Casa e cucina:Aspirapolvere e pulizia di pavimenti e finestre:Lavatappeti</t>
         </is>
       </c>
       <c r="N34" s="14" t="inlineStr">
         <is>
-          <t>Visualizza i Top 100 nella categoria Salute e</t>
+          <t>Visualizza i Top 100 nella categoria Casa e c</t>
         </is>
       </c>
       <c r="O34" s="15">
-        <v>1533</v>
+        <v>11634</v>
       </c>
       <c r="P34" s="15">
-        <v>-583</v>
+        <v>-31923</v>
       </c>
       <c r="Q34" s="16">
-        <v>-0.61</v>
+        <v>-5.81</v>
       </c>
       <c r="R34" s="17" t="inlineStr">
         <is>
-          <t>Detersivi lavaggio a macchina tappeti domestici</t>
+          <t>Lavatappeti</t>
         </is>
       </c>
       <c r="S34" s="18" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>29</t>
         </is>
       </c>
       <c r="T34" s="15">
-        <v>784</v>
-      </c>
-      <c r="U34" s="16">
-        <v>-0.06</v>
-      </c>
+        <v>115</v>
+      </c>
+      <c r="U34" s="16"/>
       <c r="V34" s="15">
-        <v>11752</v>
+        <v>11499</v>
       </c>
       <c r="W34" s="15" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>50</t>
         </is>
       </c>
       <c r="X34" s="15">
-        <v>1499</v>
+        <v>4753</v>
       </c>
       <c r="Y34" s="19">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="Z34" s="20">
-        <v>14.99</v>
+        <v>99.99</v>
       </c>
       <c r="AA34"/>
       <c r="AB34"/>
-      <c r="AC34" s="2">
-        <v>10</v>
-      </c>
+      <c r="AC34" s="2"/>
       <c r="AD34" s="19">
-        <v>9333</v>
+        <v>28</v>
       </c>
       <c r="AE34" s="15">
-        <v>109</v>
+        <v>15</v>
       </c>
       <c r="AF34" s="21">
-        <v>4.6</v>
+        <v>4</v>
       </c>
       <c r="AG34" s="22">
-        <v>0.139</v>
+        <v>0.1304</v>
       </c>
       <c r="AH34" s="20">
-        <v>5.19</v>
+        <v>9.35</v>
       </c>
       <c r="AI34" s="16">
-        <v>0.5</v>
+        <v>0.76</v>
       </c>
       <c r="AJ34"/>
       <c r="AK34" s="13" t="inlineStr">
         <is>
-          <t>2017-10-06</t>
+          <t>2026-06-04</t>
         </is>
       </c>
       <c r="AL34" s="19">
-        <v>3250</v>
+        <v>88</v>
       </c>
       <c r="AM34" s="13" t="inlineStr">
         <is>
-          <t>AMZ</t>
+          <t>NA</t>
         </is>
       </c>
       <c r="AN34" s="13"/>
@@ -15083,27 +14991,35 @@
         <v>10</v>
       </c>
       <c r="AR34" s="19">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="AS34" s="14" t="inlineStr">
         <is>
-          <t>Amazon</t>
+          <t>Lehmann HG</t>
         </is>
       </c>
       <c r="AT34" s="13" t="inlineStr">
         <is>
-          <t>AMZ</t>
-        </is>
-      </c>
-      <c r="AU34" s="13"/>
-      <c r="AV34" s="14"/>
-      <c r="AW34" s="13"/>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="AU34" s="13" t="inlineStr">
+        <is>
+          <t>PL</t>
+        </is>
+      </c>
+      <c r="AV34" s="14" t="inlineStr">
+        <is>
+          <t>Greater Poland 63-100 PL</t>
+        </is>
+      </c>
+      <c r="AW34" s="13" t="inlineStr">
+        <is>
+          <t>https://www.amazon.it/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A2WUCJY3ZYROH</t>
+        </is>
+      </c>
       <c r="AX34" s="13"/>
-      <c r="AY34" s="13" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
+      <c r="AY34" s="13"/>
       <c r="AZ34" s="13"/>
       <c r="BA34" s="13"/>
       <c r="BB34" s="13"/>
@@ -15112,63 +15028,47 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="BD34" s="13" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
+      <c r="BD34" s="13"/>
       <c r="BE34" s="13"/>
       <c r="BF34" s="13"/>
       <c r="BG34" s="13"/>
       <c r="BH34" s="14"/>
-      <c r="BI34" s="23" t="inlineStr">
-        <is>
-          <t>Scelta Amazon</t>
-        </is>
-      </c>
+      <c r="BI34" s="23"/>
       <c r="BJ34" s="23" t="inlineStr">
         <is>
-          <t>1,1 kg</t>
-        </is>
-      </c>
-      <c r="BK34" s="23" t="inlineStr">
-        <is>
-          <t>1.10 kg</t>
-        </is>
-      </c>
+          <t>4,7 Chilogrammi</t>
+        </is>
+      </c>
+      <c r="BK34" s="23"/>
       <c r="BL34" s="23" t="inlineStr">
         <is>
-          <t>7 x 12 x 23,8 cm</t>
-        </is>
-      </c>
-      <c r="BM34" s="23" t="inlineStr">
-        <is>
-          <t>7.00 x 12.00 x 23.80 cm</t>
-        </is>
-      </c>
+          <t>22P x 32l x 30H cm</t>
+        </is>
+      </c>
+      <c r="BM34" s="23"/>
       <c r="BN34" s="23" t="inlineStr">
         <is>
-          <t>1.1 kg</t>
+          <t>5.76 kg</t>
         </is>
       </c>
       <c r="BO34" s="23" t="inlineStr">
         <is>
-          <t>1.10 kg</t>
+          <t>5.76 kg</t>
         </is>
       </c>
       <c r="BP34" s="23" t="inlineStr">
         <is>
-          <t>23.5 x 11.9 x 6.9 cm</t>
+          <t>37.3 x 35.7 x 31.8 cm</t>
         </is>
       </c>
       <c r="BQ34" s="23" t="inlineStr">
         <is>
-          <t>23.50 x 11.90 x 6.90 cm</t>
+          <t>37.30 x 35.70 x 31.80 cm</t>
         </is>
       </c>
       <c r="BR34" s="13" t="inlineStr">
         <is>
-          <t>小包裹</t>
+          <t>轻型标准大件</t>
         </is>
       </c>
     </row>
@@ -15179,40 +15079,40 @@
       <c r="B35" s="13"/>
       <c r="C35" s="14" t="inlineStr">
         <is>
-          <t>B0H3LCDNGF</t>
+          <t>B0GLNFSYRW</t>
         </is>
       </c>
       <c r="D35" s="14"/>
       <c r="E35" s="14"/>
       <c r="F35" s="14" t="inlineStr">
         <is>
-          <t>LEHMANN POLSKA</t>
+          <t>Vozascly</t>
         </is>
       </c>
       <c r="G35" s="14" t="inlineStr">
         <is>
-          <t>https://www.amazon.it/stores/LEHMANN/page/F8312757-EA08-4E70-8102-256521882264?lp_asin=B0H3LCDNGF&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto&amp;bl_grd_status=override</t>
+          <t>https://www.amazon.it/s/ref=bl_dp_s_web_0?ie=UTF8&amp;search-alias=aps&amp;field-keywords=Vozascly</t>
         </is>
       </c>
       <c r="H35" s="14" t="inlineStr">
         <is>
-          <t>LEHMANN SteamWash 1800 Lavatappezzeria e Pulitore a Vapore 4 in 1, Lavatappeti e Divani con Acqua Calda 60°C e Vapore 116°C,</t>
+          <t>Vozascly F1 Lavatappeti Aspirapolvere Tessuti Divani, Pulitore per Tappeti e Tappezzeria con Aspirazione, 600W+1200W Lava e A</t>
         </is>
       </c>
       <c r="I35" s="14"/>
       <c r="J35" s="14" t="inlineStr">
         <is>
-          <t>https://www.amazon.it/dp/B0H3LCDNGF?psc=1</t>
+          <t>https://www.amazon.it/dp/B0GLNFSYRW?psc=1</t>
         </is>
       </c>
       <c r="K35" s="14" t="inlineStr">
         <is>
-          <t>https://m.media-amazon.com/images/I/41Md9nniqDL._AC_US600_.jpg</t>
+          <t>https://m.media-amazon.com/images/I/41zOwfkwiCL._AC_US600_.jpg</t>
         </is>
       </c>
       <c r="L35" s="14" t="inlineStr">
         <is>
-          <t>B0H3LCDNGF</t>
+          <t>B0GLNFSYRW</t>
         </is>
       </c>
       <c r="M35" s="14" t="inlineStr">
@@ -15226,13 +15126,13 @@
         </is>
       </c>
       <c r="O35" s="15">
-        <v>11634</v>
+        <v>8155</v>
       </c>
       <c r="P35" s="15">
-        <v>-31923</v>
+        <v>2633</v>
       </c>
       <c r="Q35" s="16">
-        <v>-5.81</v>
+        <v>0.24</v>
       </c>
       <c r="R35" s="17" t="inlineStr">
         <is>
@@ -15241,15 +15141,17 @@
       </c>
       <c r="S35" s="18" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>28</t>
         </is>
       </c>
       <c r="T35" s="15">
-        <v>115</v>
-      </c>
-      <c r="U35" s="16"/>
+        <v>90</v>
+      </c>
+      <c r="U35" s="16">
+        <v>-0.88</v>
+      </c>
       <c r="V35" s="15">
-        <v>11499</v>
+        <v>10799</v>
       </c>
       <c r="W35" s="15" t="inlineStr">
         <is>
@@ -15257,47 +15159,47 @@
         </is>
       </c>
       <c r="X35" s="15">
-        <v>4753</v>
+        <v>7280</v>
       </c>
       <c r="Y35" s="19">
         <v>1</v>
       </c>
       <c r="Z35" s="20">
-        <v>99.99</v>
+        <v>119.99</v>
       </c>
       <c r="AA35"/>
       <c r="AB35"/>
       <c r="AC35" s="2"/>
       <c r="AD35" s="19">
-        <v>28</v>
+        <v>33</v>
       </c>
       <c r="AE35" s="15">
-        <v>15</v>
+        <v>3</v>
       </c>
       <c r="AF35" s="21">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="AG35" s="22">
-        <v>0.1304</v>
+        <v>0.0333</v>
       </c>
       <c r="AH35" s="20">
-        <v>9.35</v>
+        <v>8.9</v>
       </c>
       <c r="AI35" s="16">
-        <v>0.76</v>
+        <v>0.8</v>
       </c>
       <c r="AJ35"/>
       <c r="AK35" s="13" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-02-08</t>
         </is>
       </c>
       <c r="AL35" s="19">
-        <v>88</v>
+        <v>203</v>
       </c>
       <c r="AM35" s="13" t="inlineStr">
         <is>
-          <t>NA</t>
+          <t>FBA</t>
         </is>
       </c>
       <c r="AN35" s="13"/>
@@ -15311,31 +15213,35 @@
       </c>
       <c r="AS35" s="14" t="inlineStr">
         <is>
-          <t>Lehmann HG</t>
+          <t>TEONIK IOANNIS SINGLE MEMBER P.C.</t>
         </is>
       </c>
       <c r="AT35" s="13" t="inlineStr">
         <is>
-          <t>NA</t>
+          <t>FBA</t>
         </is>
       </c>
       <c r="AU35" s="13" t="inlineStr">
         <is>
-          <t>PL</t>
+          <t>GR</t>
         </is>
       </c>
       <c r="AV35" s="14" t="inlineStr">
         <is>
-          <t>Greater Poland 63-100 PL</t>
+          <t>THESSALONIKI 54629 GR</t>
         </is>
       </c>
       <c r="AW35" s="13" t="inlineStr">
         <is>
-          <t>https://www.amazon.it/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A2WUCJY3ZYROH</t>
+          <t>https://www.amazon.it/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=AEBC603LGC1S2</t>
         </is>
       </c>
       <c r="AX35" s="13"/>
-      <c r="AY35" s="13"/>
+      <c r="AY35" s="13" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
       <c r="AZ35" s="13"/>
       <c r="BA35" s="13"/>
       <c r="BB35" s="13"/>
@@ -15349,37 +15255,45 @@
       <c r="BF35" s="13"/>
       <c r="BG35" s="13"/>
       <c r="BH35" s="14"/>
-      <c r="BI35" s="23"/>
+      <c r="BI35" s="23" t="inlineStr">
+        <is>
+          <t>Scelta Amazon</t>
+        </is>
+      </c>
       <c r="BJ35" s="23" t="inlineStr">
         <is>
-          <t>4,7 Chilogrammi</t>
-        </is>
-      </c>
-      <c r="BK35" s="23"/>
+          <t>6,71 Kilograms</t>
+        </is>
+      </c>
+      <c r="BK35" s="23" t="inlineStr">
+        <is>
+          <t>6.71 kg</t>
+        </is>
+      </c>
       <c r="BL35" s="23" t="inlineStr">
         <is>
-          <t>22P x 32l x 30H cm</t>
+          <t>10P x 25l x 18H cm</t>
         </is>
       </c>
       <c r="BM35" s="23"/>
       <c r="BN35" s="23" t="inlineStr">
         <is>
-          <t>5.76 kg</t>
+          <t>6.71 kg</t>
         </is>
       </c>
       <c r="BO35" s="23" t="inlineStr">
         <is>
-          <t>5.76 kg</t>
+          <t>6.71 kg</t>
         </is>
       </c>
       <c r="BP35" s="23" t="inlineStr">
         <is>
-          <t>37.3 x 35.7 x 31.8 cm</t>
+          <t>43.9 x 35.6 x 20.1 cm</t>
         </is>
       </c>
       <c r="BQ35" s="23" t="inlineStr">
         <is>
-          <t>37.30 x 35.70 x 31.80 cm</t>
+          <t>43.90 x 35.60 x 20.10 cm</t>
         </is>
       </c>
       <c r="BR35" s="13" t="inlineStr">
@@ -15395,40 +15309,40 @@
       <c r="B36" s="13"/>
       <c r="C36" s="14" t="inlineStr">
         <is>
-          <t>B0GLNFSYRW</t>
+          <t>B0BSHCQQ4W</t>
         </is>
       </c>
       <c r="D36" s="14"/>
       <c r="E36" s="14"/>
       <c r="F36" s="14" t="inlineStr">
         <is>
-          <t>Vozascly</t>
+          <t>H.Koenig</t>
         </is>
       </c>
       <c r="G36" s="14" t="inlineStr">
         <is>
-          <t>https://www.amazon.it/s/ref=bl_dp_s_web_0?ie=UTF8&amp;search-alias=aps&amp;field-keywords=Vozascly</t>
+          <t>https://www.amazon.it/stores/HKoenig/page/978AEC1C-8AF0-4DD0-AECD-D6014C0418DD?lp_asin=B0BSHCQQ4W&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto&amp;bl_grd_status=override</t>
         </is>
       </c>
       <c r="H36" s="14" t="inlineStr">
         <is>
-          <t>Vozascly F1 Lavatappeti Aspirapolvere Tessuti Divani, Pulitore per Tappeti e Tappezzeria con Aspirazione, 600W+1200W Lava e A</t>
+          <t>H.Koenig Pulitore smacchiatore TWT77 per tessuti:Tappeti/Divani/Poltrone/Materassi, Serbatoi acqua pulita e sporca rimovibili</t>
         </is>
       </c>
       <c r="I36" s="14"/>
       <c r="J36" s="14" t="inlineStr">
         <is>
-          <t>https://www.amazon.it/dp/B0GLNFSYRW?psc=1</t>
+          <t>https://www.amazon.it/dp/B0BSHCQQ4W?psc=1</t>
         </is>
       </c>
       <c r="K36" s="14" t="inlineStr">
         <is>
-          <t>https://m.media-amazon.com/images/I/41zOwfkwiCL._AC_US600_.jpg</t>
+          <t>https://m.media-amazon.com/images/I/41EDgJP8-JL._AC_US600_.jpg</t>
         </is>
       </c>
       <c r="L36" s="14" t="inlineStr">
         <is>
-          <t>B0GLNFSYRW</t>
+          <t>B0BSHCQQ4W</t>
         </is>
       </c>
       <c r="M36" s="14" t="inlineStr">
@@ -15442,13 +15356,13 @@
         </is>
       </c>
       <c r="O36" s="15">
-        <v>8155</v>
+        <v>19516</v>
       </c>
       <c r="P36" s="15">
-        <v>2633</v>
+        <v>-1141</v>
       </c>
       <c r="Q36" s="16">
-        <v>0.24</v>
+        <v>-0.26</v>
       </c>
       <c r="R36" s="17" t="inlineStr">
         <is>
@@ -15457,65 +15371,65 @@
       </c>
       <c r="S36" s="18" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>38</t>
         </is>
       </c>
       <c r="T36" s="15">
-        <v>90</v>
+        <v>179</v>
       </c>
       <c r="U36" s="16">
-        <v>-0.88</v>
+        <v>0.6</v>
       </c>
       <c r="V36" s="15">
-        <v>10799</v>
+        <v>10722</v>
       </c>
       <c r="W36" s="15" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>100</t>
         </is>
       </c>
       <c r="X36" s="15">
-        <v>7280</v>
+        <v>6312</v>
       </c>
       <c r="Y36" s="19">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="Z36" s="20">
-        <v>119.99</v>
+        <v>99.9</v>
       </c>
       <c r="AA36"/>
       <c r="AB36"/>
       <c r="AC36" s="2"/>
       <c r="AD36" s="19">
-        <v>33</v>
+        <v>1077</v>
       </c>
       <c r="AE36" s="15">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AF36" s="21">
         <v>4.1</v>
       </c>
       <c r="AG36" s="22">
-        <v>0.0333</v>
+        <v>0</v>
       </c>
       <c r="AH36" s="20">
-        <v>8.9</v>
+        <v>9.79</v>
       </c>
       <c r="AI36" s="16">
-        <v>0.8</v>
+        <v>0.69</v>
       </c>
       <c r="AJ36"/>
       <c r="AK36" s="13" t="inlineStr">
         <is>
-          <t>2026-02-08</t>
+          <t>2023-02-26</t>
         </is>
       </c>
       <c r="AL36" s="19">
-        <v>203</v>
+        <v>1282</v>
       </c>
       <c r="AM36" s="13" t="inlineStr">
         <is>
-          <t>FBA</t>
+          <t>NA</t>
         </is>
       </c>
       <c r="AN36" s="13"/>
@@ -15525,39 +15439,35 @@
         <v>10</v>
       </c>
       <c r="AR36" s="19">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="AS36" s="14" t="inlineStr">
         <is>
-          <t>TEONIK IOANNIS SINGLE MEMBER P.C.</t>
+          <t>HomeHome by A</t>
         </is>
       </c>
       <c r="AT36" s="13" t="inlineStr">
         <is>
-          <t>FBA</t>
+          <t>NA</t>
         </is>
       </c>
       <c r="AU36" s="13" t="inlineStr">
         <is>
-          <t>GR</t>
+          <t>FR</t>
         </is>
       </c>
       <c r="AV36" s="14" t="inlineStr">
         <is>
-          <t>THESSALONIKI 54629 GR</t>
+          <t>Paris 75001 FR</t>
         </is>
       </c>
       <c r="AW36" s="13" t="inlineStr">
         <is>
-          <t>https://www.amazon.it/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=AEBC603LGC1S2</t>
+          <t>https://www.amazon.it/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A2J1ZXSJG29176</t>
         </is>
       </c>
       <c r="AX36" s="13"/>
-      <c r="AY36" s="13" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
+      <c r="AY36" s="13"/>
       <c r="AZ36" s="13"/>
       <c r="BA36" s="13"/>
       <c r="BB36" s="13"/>
@@ -15566,50 +15476,46 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="BD36" s="13"/>
+      <c r="BD36" s="13" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
       <c r="BE36" s="13"/>
       <c r="BF36" s="13"/>
       <c r="BG36" s="13"/>
       <c r="BH36" s="14"/>
-      <c r="BI36" s="23" t="inlineStr">
-        <is>
-          <t>Scelta Amazon</t>
-        </is>
-      </c>
+      <c r="BI36" s="23"/>
       <c r="BJ36" s="23" t="inlineStr">
         <is>
-          <t>6,71 Kilograms</t>
-        </is>
-      </c>
-      <c r="BK36" s="23" t="inlineStr">
-        <is>
-          <t>6.71 kg</t>
-        </is>
-      </c>
+          <t>4 Chilogrammi</t>
+        </is>
+      </c>
+      <c r="BK36" s="23"/>
       <c r="BL36" s="23" t="inlineStr">
         <is>
-          <t>10P x 25l x 18H cm</t>
+          <t>36,5P x 24,5l x 31,8H cm</t>
         </is>
       </c>
       <c r="BM36" s="23"/>
       <c r="BN36" s="23" t="inlineStr">
         <is>
-          <t>6.71 kg</t>
+          <t>5.88 kg</t>
         </is>
       </c>
       <c r="BO36" s="23" t="inlineStr">
         <is>
-          <t>6.71 kg</t>
+          <t>5.88 kg</t>
         </is>
       </c>
       <c r="BP36" s="23" t="inlineStr">
         <is>
-          <t>43.9 x 35.6 x 20.1 cm</t>
+          <t>45 x 38 x 29 cm</t>
         </is>
       </c>
       <c r="BQ36" s="23" t="inlineStr">
         <is>
-          <t>43.90 x 35.60 x 20.10 cm</t>
+          <t>45.00 x 38.00 x 29.00 cm</t>
         </is>
       </c>
       <c r="BR36" s="13" t="inlineStr">
@@ -15625,40 +15531,40 @@
       <c r="B37" s="13"/>
       <c r="C37" s="14" t="inlineStr">
         <is>
-          <t>B0BSHCQQ4W</t>
+          <t>B0FJFDG5PY</t>
         </is>
       </c>
       <c r="D37" s="14"/>
       <c r="E37" s="14"/>
       <c r="F37" s="14" t="inlineStr">
         <is>
-          <t>H.Koenig</t>
+          <t>Akitas</t>
         </is>
       </c>
       <c r="G37" s="14" t="inlineStr">
         <is>
-          <t>https://www.amazon.it/stores/HKoenig/page/978AEC1C-8AF0-4DD0-AECD-D6014C0418DD?lp_asin=B0BSHCQQ4W&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto&amp;bl_grd_status=override</t>
+          <t>https://www.amazon.it/stores/Akitas/page/EE82F545-EF96-443C-8B75-30C504BE3C43?lp_asin=B0FJFDG5PY&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto&amp;bl_grd_status=override</t>
         </is>
       </c>
       <c r="H37" s="14" t="inlineStr">
         <is>
-          <t>H.Koenig Pulitore smacchiatore TWT77 per tessuti:Tappeti/Divani/Poltrone/Materassi, Serbatoi acqua pulita e sporca rimovibili</t>
+          <t>Akitas X7 600W Lavatappeti e Divani Lava e Asciuga, 14kPa Potente Aspirazione, Lava Tappezzeria per Auto, Moquette, Materassi</t>
         </is>
       </c>
       <c r="I37" s="14"/>
       <c r="J37" s="14" t="inlineStr">
         <is>
-          <t>https://www.amazon.it/dp/B0BSHCQQ4W?psc=1</t>
+          <t>https://www.amazon.it/dp/B0FJFDG5PY?psc=1</t>
         </is>
       </c>
       <c r="K37" s="14" t="inlineStr">
         <is>
-          <t>https://m.media-amazon.com/images/I/41EDgJP8-JL._AC_US600_.jpg</t>
+          <t>https://m.media-amazon.com/images/I/41MJX3SSe4L._AC_US600_.jpg</t>
         </is>
       </c>
       <c r="L37" s="14" t="inlineStr">
         <is>
-          <t>B0BSHCQQ4W</t>
+          <t>B0FJFDG5PY</t>
         </is>
       </c>
       <c r="M37" s="14" t="inlineStr">
@@ -15672,13 +15578,13 @@
         </is>
       </c>
       <c r="O37" s="15">
-        <v>19516</v>
+        <v>14747</v>
       </c>
       <c r="P37" s="15">
-        <v>-1141</v>
+        <v>-2799</v>
       </c>
       <c r="Q37" s="16">
-        <v>-0.26</v>
+        <v>-0.24</v>
       </c>
       <c r="R37" s="17" t="inlineStr">
         <is>
@@ -15687,37 +15593,37 @@
       </c>
       <c r="S37" s="18" t="inlineStr">
         <is>
-          <t>38</t>
+          <t>35</t>
         </is>
       </c>
       <c r="T37" s="15">
-        <v>179</v>
+        <v>124</v>
       </c>
       <c r="U37" s="16">
-        <v>0.6</v>
+        <v>0.08</v>
       </c>
       <c r="V37" s="15">
-        <v>10722</v>
+        <v>9919</v>
       </c>
       <c r="W37" s="15" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>50</t>
         </is>
       </c>
       <c r="X37" s="15">
-        <v>6312</v>
+        <v>4000</v>
       </c>
       <c r="Y37" s="19">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="Z37" s="20">
-        <v>99.9</v>
+        <v>79.99</v>
       </c>
       <c r="AA37"/>
       <c r="AB37"/>
       <c r="AC37" s="2"/>
       <c r="AD37" s="19">
-        <v>1077</v>
+        <v>568</v>
       </c>
       <c r="AE37" s="15">
         <v>0</v>
@@ -15729,23 +15635,23 @@
         <v>0</v>
       </c>
       <c r="AH37" s="20">
-        <v>9.79</v>
+        <v>5.21</v>
       </c>
       <c r="AI37" s="16">
-        <v>0.69</v>
+        <v>0.78</v>
       </c>
       <c r="AJ37"/>
       <c r="AK37" s="13" t="inlineStr">
         <is>
-          <t>2023-02-26</t>
+          <t>2025-09-20</t>
         </is>
       </c>
       <c r="AL37" s="19">
-        <v>1282</v>
+        <v>344</v>
       </c>
       <c r="AM37" s="13" t="inlineStr">
         <is>
-          <t>NA</t>
+          <t>FBA</t>
         </is>
       </c>
       <c r="AN37" s="13"/>
@@ -15755,35 +15661,43 @@
         <v>10</v>
       </c>
       <c r="AR37" s="19">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="AS37" s="14" t="inlineStr">
         <is>
-          <t>HomeHome by A</t>
+          <t>Chelsea Company Limited</t>
         </is>
       </c>
       <c r="AT37" s="13" t="inlineStr">
         <is>
-          <t>NA</t>
+          <t>FBA</t>
         </is>
       </c>
       <c r="AU37" s="13" t="inlineStr">
         <is>
-          <t>FR</t>
+          <t>CN(HK)</t>
         </is>
       </c>
       <c r="AV37" s="14" t="inlineStr">
         <is>
-          <t>Paris 75001 FR</t>
+          <t>Tin Hau Hong Kong 852 HK</t>
         </is>
       </c>
       <c r="AW37" s="13" t="inlineStr">
         <is>
-          <t>https://www.amazon.it/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A2J1ZXSJG29176</t>
-        </is>
-      </c>
-      <c r="AX37" s="13"/>
-      <c r="AY37" s="13"/>
+          <t>https://www.amazon.it/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A3ZOAHYWM588P</t>
+        </is>
+      </c>
+      <c r="AX37" s="13" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="AY37" s="13" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
       <c r="AZ37" s="13"/>
       <c r="BA37" s="13"/>
       <c r="BB37" s="13"/>
@@ -15792,51 +15706,51 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="BD37" s="13" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
+      <c r="BD37" s="13"/>
       <c r="BE37" s="13"/>
       <c r="BF37" s="13"/>
       <c r="BG37" s="13"/>
       <c r="BH37" s="14"/>
-      <c r="BI37" s="23"/>
+      <c r="BI37" s="23" t="inlineStr">
+        <is>
+          <t>Scelta Amazon</t>
+        </is>
+      </c>
       <c r="BJ37" s="23" t="inlineStr">
         <is>
-          <t>4 Chilogrammi</t>
+          <t>3,4 Chilogrammi</t>
         </is>
       </c>
       <c r="BK37" s="23"/>
       <c r="BL37" s="23" t="inlineStr">
         <is>
-          <t>36,5P x 24,5l x 31,8H cm</t>
+          <t>28P x 22l x 28H cm</t>
         </is>
       </c>
       <c r="BM37" s="23"/>
       <c r="BN37" s="23" t="inlineStr">
         <is>
-          <t>5.88 kg</t>
+          <t>4.21 kg</t>
         </is>
       </c>
       <c r="BO37" s="23" t="inlineStr">
         <is>
-          <t>5.88 kg</t>
+          <t>4.21 kg</t>
         </is>
       </c>
       <c r="BP37" s="23" t="inlineStr">
         <is>
-          <t>45 x 38 x 29 cm</t>
+          <t>44.5 x 33.7 x 19.7 cm</t>
         </is>
       </c>
       <c r="BQ37" s="23" t="inlineStr">
         <is>
-          <t>45.00 x 38.00 x 29.00 cm</t>
+          <t>44.50 x 33.70 x 19.70 cm</t>
         </is>
       </c>
       <c r="BR37" s="13" t="inlineStr">
         <is>
-          <t>轻型标准大件</t>
+          <t>标准包裹</t>
         </is>
       </c>
     </row>
@@ -15847,40 +15761,40 @@
       <c r="B38" s="13"/>
       <c r="C38" s="14" t="inlineStr">
         <is>
-          <t>B0FJFDG5PY</t>
+          <t>B0BTHFNNH1</t>
         </is>
       </c>
       <c r="D38" s="14"/>
       <c r="E38" s="14"/>
       <c r="F38" s="14" t="inlineStr">
         <is>
-          <t>Akitas</t>
+          <t>Vacmaster</t>
         </is>
       </c>
       <c r="G38" s="14" t="inlineStr">
         <is>
-          <t>https://www.amazon.it/stores/Akitas/page/EE82F545-EF96-443C-8B75-30C504BE3C43?lp_asin=B0FJFDG5PY&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto&amp;bl_grd_status=override</t>
+          <t>https://www.amazon.it/stores/VACMASTER/page/F372FF16-5498-423D-9923-A4EFB43DC86B?lp_asin=B0BTHFNNH1&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto</t>
         </is>
       </c>
       <c r="H38" s="14" t="inlineStr">
         <is>
-          <t>Akitas X7 600W Lavatappeti e Divani Lava e Asciuga, 14kPa Potente Aspirazione, Lava Tappezzeria per Auto, Moquette, Materassi</t>
+          <t>Vacmaster SCA0801 Lavatappeti Detergente per Tappezzeria MacchiesAspirapolvere umido e secco Potenza detergente Per divani,</t>
         </is>
       </c>
       <c r="I38" s="14"/>
       <c r="J38" s="14" t="inlineStr">
         <is>
-          <t>https://www.amazon.it/dp/B0FJFDG5PY?psc=1</t>
+          <t>https://www.amazon.it/dp/B0BTHFNNH1?psc=1</t>
         </is>
       </c>
       <c r="K38" s="14" t="inlineStr">
         <is>
-          <t>https://m.media-amazon.com/images/I/41MJX3SSe4L._AC_US600_.jpg</t>
+          <t>https://images-na.ssl-images-amazon.com/images/I/81ygbNkGjPL._AC_US600_.jpg</t>
         </is>
       </c>
       <c r="L38" s="14" t="inlineStr">
         <is>
-          <t>B0FJFDG5PY</t>
+          <t>B0BTHFNNH1</t>
         </is>
       </c>
       <c r="M38" s="14" t="inlineStr">
@@ -15894,13 +15808,13 @@
         </is>
       </c>
       <c r="O38" s="15">
-        <v>14747</v>
+        <v>9542</v>
       </c>
       <c r="P38" s="15">
-        <v>-2799</v>
+        <v>25275</v>
       </c>
       <c r="Q38" s="16">
-        <v>-0.24</v>
+        <v>0.73</v>
       </c>
       <c r="R38" s="17" t="inlineStr">
         <is>
@@ -15909,65 +15823,59 @@
       </c>
       <c r="S38" s="18" t="inlineStr">
         <is>
-          <t>35</t>
+          <t>25</t>
         </is>
       </c>
       <c r="T38" s="15">
-        <v>124</v>
+        <v>71</v>
       </c>
       <c r="U38" s="16">
-        <v>0.08</v>
+        <v>0.87</v>
       </c>
       <c r="V38" s="15">
-        <v>9919</v>
-      </c>
-      <c r="W38" s="15" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="X38" s="15">
-        <v>4000</v>
-      </c>
+        <v>7186</v>
+      </c>
+      <c r="W38" s="15"/>
+      <c r="X38" s="15"/>
       <c r="Y38" s="19">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="Z38" s="20">
-        <v>79.99</v>
+        <v>101.21</v>
       </c>
       <c r="AA38"/>
       <c r="AB38"/>
       <c r="AC38" s="2"/>
       <c r="AD38" s="19">
-        <v>568</v>
+        <v>500</v>
       </c>
       <c r="AE38" s="15">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="AF38" s="21">
-        <v>4.1</v>
+        <v>4.5</v>
       </c>
       <c r="AG38" s="22">
-        <v>0</v>
+        <v>0.0704</v>
       </c>
       <c r="AH38" s="20">
-        <v>5.21</v>
+        <v>9.35</v>
       </c>
       <c r="AI38" s="16">
-        <v>0.78</v>
+        <v>0.76</v>
       </c>
       <c r="AJ38"/>
       <c r="AK38" s="13" t="inlineStr">
         <is>
-          <t>2025-09-20</t>
+          <t>2023-02-19</t>
         </is>
       </c>
       <c r="AL38" s="19">
-        <v>344</v>
+        <v>1289</v>
       </c>
       <c r="AM38" s="13" t="inlineStr">
         <is>
-          <t>FBA</t>
+          <t>AMZ</t>
         </is>
       </c>
       <c r="AN38" s="13"/>
@@ -15981,34 +15889,18 @@
       </c>
       <c r="AS38" s="14" t="inlineStr">
         <is>
-          <t>Chelsea Company Limited</t>
+          <t>Amazon</t>
         </is>
       </c>
       <c r="AT38" s="13" t="inlineStr">
         <is>
-          <t>FBA</t>
-        </is>
-      </c>
-      <c r="AU38" s="13" t="inlineStr">
-        <is>
-          <t>CN(HK)</t>
-        </is>
-      </c>
-      <c r="AV38" s="14" t="inlineStr">
-        <is>
-          <t>Tin Hau Hong Kong 852 HK</t>
-        </is>
-      </c>
-      <c r="AW38" s="13" t="inlineStr">
-        <is>
-          <t>https://www.amazon.it/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A3ZOAHYWM588P</t>
-        </is>
-      </c>
-      <c r="AX38" s="13" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
+          <t>AMZ</t>
+        </is>
+      </c>
+      <c r="AU38" s="13"/>
+      <c r="AV38" s="14"/>
+      <c r="AW38" s="13"/>
+      <c r="AX38" s="13"/>
       <c r="AY38" s="13" t="inlineStr">
         <is>
           <t>Y</t>
@@ -16034,39 +15926,47 @@
       </c>
       <c r="BJ38" s="23" t="inlineStr">
         <is>
-          <t>3,4 Chilogrammi</t>
-        </is>
-      </c>
-      <c r="BK38" s="23"/>
+          <t>6.4 kg</t>
+        </is>
+      </c>
+      <c r="BK38" s="23" t="inlineStr">
+        <is>
+          <t>6.40 kg</t>
+        </is>
+      </c>
       <c r="BL38" s="23" t="inlineStr">
         <is>
-          <t>28P x 22l x 28H cm</t>
-        </is>
-      </c>
-      <c r="BM38" s="23"/>
+          <t>38.5 x 26 x 44 cm</t>
+        </is>
+      </c>
+      <c r="BM38" s="23" t="inlineStr">
+        <is>
+          <t>38.50 x 26.00 x 44.00 cm</t>
+        </is>
+      </c>
       <c r="BN38" s="23" t="inlineStr">
         <is>
-          <t>4.21 kg</t>
+          <t>6.25 kg</t>
         </is>
       </c>
       <c r="BO38" s="23" t="inlineStr">
         <is>
-          <t>4.21 kg</t>
+          <t>6.25 kg</t>
         </is>
       </c>
       <c r="BP38" s="23" t="inlineStr">
         <is>
-          <t>44.5 x 33.7 x 19.7 cm</t>
+          <t>42.7 x 38.5 x 25.4 cm</t>
         </is>
       </c>
       <c r="BQ38" s="23" t="inlineStr">
         <is>
-          <t>44.50 x 33.70 x 19.70 cm</t>
+          <t>42.70 x 38.50 x 25.40 cm</t>
         </is>
       </c>
       <c r="BR38" s="13" t="inlineStr">
         <is>
-          <t>标准包裹</t>
+          <t>轻型标准大件</t>
         </is>
       </c>
     </row>
@@ -16077,40 +15977,40 @@
       <c r="B39" s="13"/>
       <c r="C39" s="14" t="inlineStr">
         <is>
-          <t>B0BTHFNNH1</t>
+          <t>B0D2HFLM1C</t>
         </is>
       </c>
       <c r="D39" s="14"/>
       <c r="E39" s="14"/>
       <c r="F39" s="14" t="inlineStr">
         <is>
-          <t>Vacmaster</t>
+          <t>HAUSHOF</t>
         </is>
       </c>
       <c r="G39" s="14" t="inlineStr">
         <is>
-          <t>https://www.amazon.it/stores/VACMASTER/page/F372FF16-5498-423D-9923-A4EFB43DC86B?lp_asin=B0BTHFNNH1&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto</t>
+          <t>https://www.amazon.it/stores/HAUSHOF/page/9EE9CFD0-E18C-46CA-98BB-FA1050DF3283?lp_asin=B0D2HFLM1C&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto</t>
         </is>
       </c>
       <c r="H39" s="14" t="inlineStr">
         <is>
-          <t>Vacmaster SCA0801 Lavatappeti Detergente per Tappezzeria MacchiesAspirapolvere umido e secco Potenza detergente Per divani,</t>
+          <t>HAUSHOF StainZapper Pro - Lavatappeti Portatile 450W 11,5kPas1,5L lava tappezzeria ad Acqua con Detergente e Spazzola per G</t>
         </is>
       </c>
       <c r="I39" s="14"/>
       <c r="J39" s="14" t="inlineStr">
         <is>
-          <t>https://www.amazon.it/dp/B0BTHFNNH1?psc=1</t>
+          <t>https://www.amazon.it/dp/B0D2HFLM1C?psc=1</t>
         </is>
       </c>
       <c r="K39" s="14" t="inlineStr">
         <is>
-          <t>https://images-na.ssl-images-amazon.com/images/I/81ygbNkGjPL._AC_US600_.jpg</t>
+          <t>https://images-na.ssl-images-amazon.com/images/I/71cgtv2WdbL._AC_US600_.jpg</t>
         </is>
       </c>
       <c r="L39" s="14" t="inlineStr">
         <is>
-          <t>B0BTHFNNH1</t>
+          <t>B0D2HFLM1C</t>
         </is>
       </c>
       <c r="M39" s="14" t="inlineStr">
@@ -16124,13 +16024,13 @@
         </is>
       </c>
       <c r="O39" s="15">
-        <v>9542</v>
+        <v>3435</v>
       </c>
       <c r="P39" s="15">
-        <v>25275</v>
+        <v>19883</v>
       </c>
       <c r="Q39" s="16">
-        <v>0.73</v>
+        <v>0.85</v>
       </c>
       <c r="R39" s="17" t="inlineStr">
         <is>
@@ -16139,55 +16039,61 @@
       </c>
       <c r="S39" s="18" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>17</t>
         </is>
       </c>
       <c r="T39" s="15">
-        <v>71</v>
+        <v>86</v>
       </c>
       <c r="U39" s="16">
-        <v>0.87</v>
+        <v>-0.58</v>
       </c>
       <c r="V39" s="15">
-        <v>7186</v>
-      </c>
-      <c r="W39" s="15"/>
-      <c r="X39" s="15"/>
+        <v>6879</v>
+      </c>
+      <c r="W39" s="15" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="X39" s="15">
+        <v>4409</v>
+      </c>
       <c r="Y39" s="19">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="Z39" s="20">
-        <v>101.21</v>
+        <v>79.99</v>
       </c>
       <c r="AA39"/>
       <c r="AB39"/>
       <c r="AC39" s="2"/>
       <c r="AD39" s="19">
-        <v>500</v>
+        <v>740</v>
       </c>
       <c r="AE39" s="15">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="AF39" s="21">
-        <v>4.5</v>
+        <v>4.3</v>
       </c>
       <c r="AG39" s="22">
-        <v>0.0704</v>
+        <v>0.0349</v>
       </c>
       <c r="AH39" s="20">
-        <v>9.35</v>
+        <v>5.18</v>
       </c>
       <c r="AI39" s="16">
-        <v>0.76</v>
+        <v>0.79</v>
       </c>
       <c r="AJ39"/>
       <c r="AK39" s="13" t="inlineStr">
         <is>
-          <t>2023-02-19</t>
+          <t>2024-07-26</t>
         </is>
       </c>
       <c r="AL39" s="19">
-        <v>1289</v>
+        <v>766</v>
       </c>
       <c r="AM39" s="13" t="inlineStr">
         <is>
@@ -16201,7 +16107,7 @@
         <v>10</v>
       </c>
       <c r="AR39" s="19">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AS39" s="14" t="inlineStr">
         <is>
@@ -16230,7 +16136,11 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="BD39" s="13"/>
+      <c r="BD39" s="13" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
       <c r="BE39" s="13"/>
       <c r="BF39" s="13"/>
       <c r="BG39" s="13"/>
@@ -16242,47 +16152,47 @@
       </c>
       <c r="BJ39" s="23" t="inlineStr">
         <is>
-          <t>6.4 kg</t>
+          <t>3.85 kg</t>
         </is>
       </c>
       <c r="BK39" s="23" t="inlineStr">
         <is>
-          <t>6.40 kg</t>
+          <t>3.85 kg</t>
         </is>
       </c>
       <c r="BL39" s="23" t="inlineStr">
         <is>
-          <t>38.5 x 26 x 44 cm</t>
+          <t>19.6 x 38.5 x 30 cm</t>
         </is>
       </c>
       <c r="BM39" s="23" t="inlineStr">
         <is>
-          <t>38.50 x 26.00 x 44.00 cm</t>
+          <t>19.60 x 38.50 x 30.00 cm</t>
         </is>
       </c>
       <c r="BN39" s="23" t="inlineStr">
         <is>
-          <t>6.25 kg</t>
+          <t>5.68 kg</t>
         </is>
       </c>
       <c r="BO39" s="23" t="inlineStr">
         <is>
-          <t>6.25 kg</t>
+          <t>5.68 kg</t>
         </is>
       </c>
       <c r="BP39" s="23" t="inlineStr">
         <is>
-          <t>42.7 x 38.5 x 25.4 cm</t>
+          <t>44.4 x 33.9 x 20 cm</t>
         </is>
       </c>
       <c r="BQ39" s="23" t="inlineStr">
         <is>
-          <t>42.70 x 38.50 x 25.40 cm</t>
+          <t>44.40 x 33.90 x 20.00 cm</t>
         </is>
       </c>
       <c r="BR39" s="13" t="inlineStr">
         <is>
-          <t>轻型标准大件</t>
+          <t>标准包裹</t>
         </is>
       </c>
     </row>
@@ -16293,40 +16203,40 @@
       <c r="B40" s="13"/>
       <c r="C40" s="14" t="inlineStr">
         <is>
-          <t>B0D2HFLM1C</t>
+          <t>B0FHB8RB8F</t>
         </is>
       </c>
       <c r="D40" s="14"/>
       <c r="E40" s="14"/>
       <c r="F40" s="14" t="inlineStr">
         <is>
-          <t>HAUSHOF</t>
+          <t>Cecotec</t>
         </is>
       </c>
       <c r="G40" s="14" t="inlineStr">
         <is>
-          <t>https://www.amazon.it/stores/HAUSHOF/page/9EE9CFD0-E18C-46CA-98BB-FA1050DF3283?lp_asin=B0D2HFLM1C&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto</t>
+          <t>https://www.amazon.it/Cecotec/b/ref=bl_dp_s_web_19986335031?ie=UTF8&amp;node=19986335031&amp;field-lbr_brands_browse-bin=Cecotec</t>
         </is>
       </c>
       <c r="H40" s="14" t="inlineStr">
         <is>
-          <t>HAUSHOF StainZapper Pro - Lavatappeti Portatile 450W 11,5kPas1,5L lava tappezzeria ad Acqua con Detergente e Spazzola per G</t>
+          <t>Cecotec Lavatappeti Aspirapolvere con Cavo Conga 7000 Carpet&amp;Spot Clean Steam. Max. 1700 W, Vapore, Serbatoio Acqua Pulita 16</t>
         </is>
       </c>
       <c r="I40" s="14"/>
       <c r="J40" s="14" t="inlineStr">
         <is>
-          <t>https://www.amazon.it/dp/B0D2HFLM1C?psc=1</t>
+          <t>https://www.amazon.it/dp/B0FHB8RB8F?psc=1</t>
         </is>
       </c>
       <c r="K40" s="14" t="inlineStr">
         <is>
-          <t>https://images-na.ssl-images-amazon.com/images/I/71cgtv2WdbL._AC_US600_.jpg</t>
+          <t>https://m.media-amazon.com/images/I/411-YObj2pL._AC_US600_.jpg</t>
         </is>
       </c>
       <c r="L40" s="14" t="inlineStr">
         <is>
-          <t>B0D2HFLM1C</t>
+          <t>B0FHB8RB8F</t>
         </is>
       </c>
       <c r="M40" s="14" t="inlineStr">
@@ -16340,13 +16250,13 @@
         </is>
       </c>
       <c r="O40" s="15">
-        <v>3435</v>
+        <v>13823</v>
       </c>
       <c r="P40" s="15">
-        <v>19883</v>
+        <v>9568</v>
       </c>
       <c r="Q40" s="16">
-        <v>0.85</v>
+        <v>0.5</v>
       </c>
       <c r="R40" s="17" t="inlineStr">
         <is>
@@ -16355,61 +16265,55 @@
       </c>
       <c r="S40" s="18" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>31</t>
         </is>
       </c>
       <c r="T40" s="15">
-        <v>86</v>
+        <v>50</v>
       </c>
       <c r="U40" s="16">
-        <v>-0.58</v>
+        <v>0.13</v>
       </c>
       <c r="V40" s="15">
-        <v>6879</v>
-      </c>
-      <c r="W40" s="15" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="X40" s="15">
-        <v>4409</v>
-      </c>
+        <v>6450</v>
+      </c>
+      <c r="W40" s="15"/>
+      <c r="X40" s="15"/>
       <c r="Y40" s="19">
         <v>2</v>
       </c>
       <c r="Z40" s="20">
-        <v>79.99</v>
+        <v>129</v>
       </c>
       <c r="AA40"/>
       <c r="AB40"/>
       <c r="AC40" s="2"/>
       <c r="AD40" s="19">
-        <v>740</v>
+        <v>81</v>
       </c>
       <c r="AE40" s="15">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="AF40" s="21">
         <v>4.3</v>
       </c>
       <c r="AG40" s="22">
-        <v>0.0349</v>
+        <v>0.16</v>
       </c>
       <c r="AH40" s="20">
-        <v>5.18</v>
+        <v>9.35</v>
       </c>
       <c r="AI40" s="16">
-        <v>0.79</v>
+        <v>0.78</v>
       </c>
       <c r="AJ40"/>
       <c r="AK40" s="13" t="inlineStr">
         <is>
-          <t>2024-07-26</t>
+          <t>2025-07-30</t>
         </is>
       </c>
       <c r="AL40" s="19">
-        <v>766</v>
+        <v>396</v>
       </c>
       <c r="AM40" s="13" t="inlineStr">
         <is>
@@ -16423,7 +16327,7 @@
         <v>10</v>
       </c>
       <c r="AR40" s="19">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="AS40" s="14" t="inlineStr">
         <is>
@@ -16468,47 +16372,39 @@
       </c>
       <c r="BJ40" s="23" t="inlineStr">
         <is>
-          <t>3.85 kg</t>
-        </is>
-      </c>
-      <c r="BK40" s="23" t="inlineStr">
-        <is>
-          <t>3.85 kg</t>
-        </is>
-      </c>
+          <t>4,34 Chilogrammi</t>
+        </is>
+      </c>
+      <c r="BK40" s="23"/>
       <c r="BL40" s="23" t="inlineStr">
         <is>
-          <t>19.6 x 38.5 x 30 cm</t>
-        </is>
-      </c>
-      <c r="BM40" s="23" t="inlineStr">
-        <is>
-          <t>19.60 x 38.50 x 30.00 cm</t>
-        </is>
-      </c>
+          <t>24P x 32l x 30H cm</t>
+        </is>
+      </c>
+      <c r="BM40" s="23"/>
       <c r="BN40" s="23" t="inlineStr">
         <is>
-          <t>5.68 kg</t>
+          <t>5.91 kg</t>
         </is>
       </c>
       <c r="BO40" s="23" t="inlineStr">
         <is>
-          <t>5.68 kg</t>
+          <t>5.91 kg</t>
         </is>
       </c>
       <c r="BP40" s="23" t="inlineStr">
         <is>
-          <t>44.4 x 33.9 x 20 cm</t>
+          <t>41.3 x 36.4 x 28.8 cm</t>
         </is>
       </c>
       <c r="BQ40" s="23" t="inlineStr">
         <is>
-          <t>44.40 x 33.90 x 20.00 cm</t>
+          <t>41.30 x 36.40 x 28.80 cm</t>
         </is>
       </c>
       <c r="BR40" s="13" t="inlineStr">
         <is>
-          <t>标准包裹</t>
+          <t>轻型标准大件</t>
         </is>
       </c>
     </row>
@@ -16519,40 +16415,40 @@
       <c r="B41" s="13"/>
       <c r="C41" s="14" t="inlineStr">
         <is>
-          <t>B0FHB8RB8F</t>
+          <t>B0CLYF3DMZ</t>
         </is>
       </c>
       <c r="D41" s="14"/>
       <c r="E41" s="14"/>
       <c r="F41" s="14" t="inlineStr">
         <is>
-          <t>Cecotec</t>
+          <t>LEHMANN POLSKA</t>
         </is>
       </c>
       <c r="G41" s="14" t="inlineStr">
         <is>
-          <t>https://www.amazon.it/Cecotec/b/ref=bl_dp_s_web_19986335031?ie=UTF8&amp;node=19986335031&amp;field-lbr_brands_browse-bin=Cecotec</t>
+          <t>https://www.amazon.it/stores/LEHMANN/page/F8312757-EA08-4E70-8102-256521882264?lp_asin=B0CLYF3DMZ&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto&amp;bl_grd_status=override</t>
         </is>
       </c>
       <c r="H41" s="14" t="inlineStr">
         <is>
-          <t>Cecotec Lavatappeti Aspirapolvere con Cavo Conga 7000 Carpet&amp;Spot Clean Steam. Max. 1700 W, Vapore, Serbatoio Acqua Pulita 16</t>
+          <t>LEHMANN Prowash Lavatappeti Professionale, 2000 W, Lava Tappezzeria Potente con 2 Serbatoi - Acqua Pulita 3L e Sporca 1,5L, T</t>
         </is>
       </c>
       <c r="I41" s="14"/>
       <c r="J41" s="14" t="inlineStr">
         <is>
-          <t>https://www.amazon.it/dp/B0FHB8RB8F?psc=1</t>
+          <t>https://www.amazon.it/dp/B0CLYF3DMZ?psc=1</t>
         </is>
       </c>
       <c r="K41" s="14" t="inlineStr">
         <is>
-          <t>https://m.media-amazon.com/images/I/411-YObj2pL._AC_US600_.jpg</t>
+          <t>https://m.media-amazon.com/images/I/41IUxMxofsL._AC_US600_.jpg</t>
         </is>
       </c>
       <c r="L41" s="14" t="inlineStr">
         <is>
-          <t>B0FHB8RB8F</t>
+          <t>B0CLYF3DMZ</t>
         </is>
       </c>
       <c r="M41" s="14" t="inlineStr">
@@ -16566,13 +16462,13 @@
         </is>
       </c>
       <c r="O41" s="15">
-        <v>13823</v>
+        <v>20591</v>
       </c>
       <c r="P41" s="15">
-        <v>9568</v>
+        <v>-543</v>
       </c>
       <c r="Q41" s="16">
-        <v>0.5</v>
+        <v>-0.02</v>
       </c>
       <c r="R41" s="17" t="inlineStr">
         <is>
@@ -16581,59 +16477,59 @@
       </c>
       <c r="S41" s="18" t="inlineStr">
         <is>
-          <t>31</t>
+          <t>40</t>
         </is>
       </c>
       <c r="T41" s="15">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="U41" s="16">
-        <v>0.13</v>
+        <v>-0.44</v>
       </c>
       <c r="V41" s="15">
-        <v>6450</v>
+        <v>5433</v>
       </c>
       <c r="W41" s="15"/>
       <c r="X41" s="15"/>
       <c r="Y41" s="19">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Z41" s="20">
-        <v>129</v>
+        <v>104.49</v>
       </c>
       <c r="AA41"/>
       <c r="AB41"/>
       <c r="AC41" s="2"/>
       <c r="AD41" s="19">
-        <v>81</v>
+        <v>382</v>
       </c>
       <c r="AE41" s="15">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="AF41" s="21">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="AG41" s="22">
-        <v>0.16</v>
+        <v>0.2692</v>
       </c>
       <c r="AH41" s="20">
-        <v>9.35</v>
+        <v>10.24</v>
       </c>
       <c r="AI41" s="16">
-        <v>0.78</v>
+        <v>0.75</v>
       </c>
       <c r="AJ41"/>
       <c r="AK41" s="13" t="inlineStr">
         <is>
-          <t>2025-07-30</t>
+          <t>2024-03-20</t>
         </is>
       </c>
       <c r="AL41" s="19">
-        <v>396</v>
+        <v>893</v>
       </c>
       <c r="AM41" s="13" t="inlineStr">
         <is>
-          <t>AMZ</t>
+          <t>FBM</t>
         </is>
       </c>
       <c r="AN41" s="13"/>
@@ -16643,21 +16539,33 @@
         <v>10</v>
       </c>
       <c r="AR41" s="19">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="AS41" s="14" t="inlineStr">
         <is>
-          <t>Amazon</t>
+          <t>Lehmann HG</t>
         </is>
       </c>
       <c r="AT41" s="13" t="inlineStr">
         <is>
-          <t>AMZ</t>
-        </is>
-      </c>
-      <c r="AU41" s="13"/>
-      <c r="AV41" s="14"/>
-      <c r="AW41" s="13"/>
+          <t>FBM</t>
+        </is>
+      </c>
+      <c r="AU41" s="13" t="inlineStr">
+        <is>
+          <t>PL</t>
+        </is>
+      </c>
+      <c r="AV41" s="14" t="inlineStr">
+        <is>
+          <t>Greater Poland 63-100 PL</t>
+        </is>
+      </c>
+      <c r="AW41" s="13" t="inlineStr">
+        <is>
+          <t>https://www.amazon.it/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A2WUCJY3ZYROH</t>
+        </is>
+      </c>
       <c r="AX41" s="13"/>
       <c r="AY41" s="13" t="inlineStr">
         <is>
@@ -16672,11 +16580,7 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="BD41" s="13" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
+      <c r="BD41" s="13"/>
       <c r="BE41" s="13"/>
       <c r="BF41" s="13"/>
       <c r="BG41" s="13"/>
@@ -16688,34 +16592,34 @@
       </c>
       <c r="BJ41" s="23" t="inlineStr">
         <is>
-          <t>4,34 Chilogrammi</t>
+          <t>6,2 Chilogrammi</t>
         </is>
       </c>
       <c r="BK41" s="23"/>
       <c r="BL41" s="23" t="inlineStr">
         <is>
-          <t>24P x 32l x 30H cm</t>
+          <t>51,3P x 27,5l x 28,8H cm</t>
         </is>
       </c>
       <c r="BM41" s="23"/>
       <c r="BN41" s="23" t="inlineStr">
         <is>
-          <t>5.91 kg</t>
+          <t>7.77 kg</t>
         </is>
       </c>
       <c r="BO41" s="23" t="inlineStr">
         <is>
-          <t>5.91 kg</t>
+          <t>7.77 kg</t>
         </is>
       </c>
       <c r="BP41" s="23" t="inlineStr">
         <is>
-          <t>41.3 x 36.4 x 28.8 cm</t>
+          <t>54.8 x 37.1 x 30.8 cm</t>
         </is>
       </c>
       <c r="BQ41" s="23" t="inlineStr">
         <is>
-          <t>41.30 x 36.40 x 28.80 cm</t>
+          <t>54.80 x 37.10 x 30.80 cm</t>
         </is>
       </c>
       <c r="BR41" s="13" t="inlineStr">
@@ -16731,40 +16635,40 @@
       <c r="B42" s="13"/>
       <c r="C42" s="14" t="inlineStr">
         <is>
-          <t>B0CLYF3DMZ</t>
+          <t>B0GH6TBJVW</t>
         </is>
       </c>
       <c r="D42" s="14"/>
       <c r="E42" s="14"/>
       <c r="F42" s="14" t="inlineStr">
         <is>
-          <t>LEHMANN POLSKA</t>
+          <t>Kitcanis</t>
         </is>
       </c>
       <c r="G42" s="14" t="inlineStr">
         <is>
-          <t>https://www.amazon.it/stores/LEHMANN/page/F8312757-EA08-4E70-8102-256521882264?lp_asin=B0CLYF3DMZ&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto&amp;bl_grd_status=override</t>
+          <t>https://www.amazon.it/s/ref=bl_dp_s_web_0?ie=UTF8&amp;search-alias=aps&amp;field-keywords=Kitcanis</t>
         </is>
       </c>
       <c r="H42" s="14" t="inlineStr">
         <is>
-          <t>LEHMANN Prowash Lavatappeti Professionale, 2000 W, Lava Tappezzeria Potente con 2 Serbatoi - Acqua Pulita 3L e Sporca 1,5L, T</t>
+          <t>Kitcanis Lavatappeti e Divani Lava e Asciuga 17KPa 600W, Pulitore Tessuti Compatto con 4 Accessori, Serbatoi Rimovibili 1.1L/</t>
         </is>
       </c>
       <c r="I42" s="14"/>
       <c r="J42" s="14" t="inlineStr">
         <is>
-          <t>https://www.amazon.it/dp/B0CLYF3DMZ?psc=1</t>
+          <t>https://www.amazon.it/dp/B0GH6TBJVW?psc=1</t>
         </is>
       </c>
       <c r="K42" s="14" t="inlineStr">
         <is>
-          <t>https://m.media-amazon.com/images/I/41IUxMxofsL._AC_US600_.jpg</t>
+          <t>https://m.media-amazon.com/images/I/51LdyRohTNL._AC_US600_.jpg</t>
         </is>
       </c>
       <c r="L42" s="14" t="inlineStr">
         <is>
-          <t>B0CLYF3DMZ</t>
+          <t>B0GH6TBJVW</t>
         </is>
       </c>
       <c r="M42" s="14" t="inlineStr">
@@ -16778,13 +16682,13 @@
         </is>
       </c>
       <c r="O42" s="15">
-        <v>20591</v>
+        <v>13837</v>
       </c>
       <c r="P42" s="15">
-        <v>-543</v>
+        <v>28448</v>
       </c>
       <c r="Q42" s="16">
-        <v>-0.02</v>
+        <v>0.67</v>
       </c>
       <c r="R42" s="17" t="inlineStr">
         <is>
@@ -16793,17 +16697,17 @@
       </c>
       <c r="S42" s="18" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>32</t>
         </is>
       </c>
       <c r="T42" s="15">
-        <v>52</v>
+        <v>67</v>
       </c>
       <c r="U42" s="16">
-        <v>-0.44</v>
+        <v>-0.25</v>
       </c>
       <c r="V42" s="15">
-        <v>5433</v>
+        <v>4991</v>
       </c>
       <c r="W42" s="15"/>
       <c r="X42" s="15"/>
@@ -16811,41 +16715,41 @@
         <v>1</v>
       </c>
       <c r="Z42" s="20">
-        <v>104.49</v>
+        <v>74.49</v>
       </c>
       <c r="AA42"/>
       <c r="AB42"/>
       <c r="AC42" s="2"/>
       <c r="AD42" s="19">
-        <v>382</v>
+        <v>85</v>
       </c>
       <c r="AE42" s="15">
-        <v>14</v>
+        <v>4</v>
       </c>
       <c r="AF42" s="21">
         <v>4.2</v>
       </c>
       <c r="AG42" s="22">
-        <v>0.2692</v>
+        <v>0.059699999999999996</v>
       </c>
       <c r="AH42" s="20">
-        <v>10.24</v>
+        <v>5.49</v>
       </c>
       <c r="AI42" s="16">
-        <v>0.75</v>
+        <v>0.79</v>
       </c>
       <c r="AJ42"/>
       <c r="AK42" s="13" t="inlineStr">
         <is>
-          <t>2024-03-20</t>
+          <t>2026-04-10</t>
         </is>
       </c>
       <c r="AL42" s="19">
-        <v>893</v>
+        <v>142</v>
       </c>
       <c r="AM42" s="13" t="inlineStr">
         <is>
-          <t>FBM</t>
+          <t>FBA</t>
         </is>
       </c>
       <c r="AN42" s="13"/>
@@ -16855,39 +16759,35 @@
         <v>10</v>
       </c>
       <c r="AR42" s="19">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="AS42" s="14" t="inlineStr">
         <is>
-          <t>Lehmann HG</t>
+          <t>BingBon</t>
         </is>
       </c>
       <c r="AT42" s="13" t="inlineStr">
         <is>
-          <t>FBM</t>
+          <t>FBA</t>
         </is>
       </c>
       <c r="AU42" s="13" t="inlineStr">
         <is>
-          <t>PL</t>
+          <t>CN</t>
         </is>
       </c>
       <c r="AV42" s="14" t="inlineStr">
         <is>
-          <t>Greater Poland 63-100 PL</t>
+          <t>青岛市 李沧区 山东省 266041 CN</t>
         </is>
       </c>
       <c r="AW42" s="13" t="inlineStr">
         <is>
-          <t>https://www.amazon.it/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A2WUCJY3ZYROH</t>
+          <t>https://www.amazon.it/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A3SC5MLKO5B7LX</t>
         </is>
       </c>
       <c r="AX42" s="13"/>
-      <c r="AY42" s="13" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
+      <c r="AY42" s="13"/>
       <c r="AZ42" s="13"/>
       <c r="BA42" s="13"/>
       <c r="BB42" s="13"/>
@@ -16896,51 +16796,59 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="BD42" s="13"/>
+      <c r="BD42" s="13" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
       <c r="BE42" s="13"/>
       <c r="BF42" s="13"/>
       <c r="BG42" s="13"/>
       <c r="BH42" s="14"/>
-      <c r="BI42" s="23" t="inlineStr">
-        <is>
-          <t>Scelta Amazon</t>
-        </is>
-      </c>
+      <c r="BI42" s="23"/>
       <c r="BJ42" s="23" t="inlineStr">
         <is>
-          <t>6,2 Chilogrammi</t>
-        </is>
-      </c>
-      <c r="BK42" s="23"/>
+          <t>4,7 Kilograms</t>
+        </is>
+      </c>
+      <c r="BK42" s="23" t="inlineStr">
+        <is>
+          <t>4.70 kg</t>
+        </is>
+      </c>
       <c r="BL42" s="23" t="inlineStr">
         <is>
-          <t>51,3P x 27,5l x 28,8H cm</t>
-        </is>
-      </c>
-      <c r="BM42" s="23"/>
+          <t>23 x 43 x 32 cm</t>
+        </is>
+      </c>
+      <c r="BM42" s="23" t="inlineStr">
+        <is>
+          <t>23.00 x 43.00 x 32.00 cm</t>
+        </is>
+      </c>
       <c r="BN42" s="23" t="inlineStr">
         <is>
-          <t>7.77 kg</t>
+          <t>4.7 kg</t>
         </is>
       </c>
       <c r="BO42" s="23" t="inlineStr">
         <is>
-          <t>7.77 kg</t>
+          <t>4.70 kg</t>
         </is>
       </c>
       <c r="BP42" s="23" t="inlineStr">
         <is>
-          <t>54.8 x 37.1 x 30.8 cm</t>
+          <t>43.6 x 32.6 x 23.4 cm</t>
         </is>
       </c>
       <c r="BQ42" s="23" t="inlineStr">
         <is>
-          <t>54.80 x 37.10 x 30.80 cm</t>
+          <t>43.60 x 32.60 x 23.40 cm</t>
         </is>
       </c>
       <c r="BR42" s="13" t="inlineStr">
         <is>
-          <t>轻型标准大件</t>
+          <t>标准包裹</t>
         </is>
       </c>
     </row>
@@ -16951,40 +16859,40 @@
       <c r="B43" s="13"/>
       <c r="C43" s="14" t="inlineStr">
         <is>
-          <t>B0GH6TBJVW</t>
+          <t>B0BPZJSXCQ</t>
         </is>
       </c>
       <c r="D43" s="14"/>
       <c r="E43" s="14"/>
       <c r="F43" s="14" t="inlineStr">
         <is>
-          <t>Kitcanis</t>
+          <t>Cecotec</t>
         </is>
       </c>
       <c r="G43" s="14" t="inlineStr">
         <is>
-          <t>https://www.amazon.it/s/ref=bl_dp_s_web_0?ie=UTF8&amp;search-alias=aps&amp;field-keywords=Kitcanis</t>
+          <t>https://www.amazon.it/Cecotec/b/ref=bl_dp_s_web_19986335031?ie=UTF8&amp;node=19986335031&amp;field-lbr_brands_browse-bin=Cecotec</t>
         </is>
       </c>
       <c r="H43" s="14" t="inlineStr">
         <is>
-          <t>Kitcanis Lavatappeti e Divani Lava e Asciuga 17KPa 600W, Pulitore Tessuti Compatto con 4 Accessori, Serbatoi Rimovibili 1.1L/</t>
+          <t>Cecotec Aspirapolvere Lava Tappeti Conga 3000 Carpetclean, 3in1:Spruzza, Pulisce e Aspira, 400W, 2 Serbatoi - Acqua Pulita e</t>
         </is>
       </c>
       <c r="I43" s="14"/>
       <c r="J43" s="14" t="inlineStr">
         <is>
-          <t>https://www.amazon.it/dp/B0GH6TBJVW?psc=1</t>
+          <t>https://www.amazon.it/dp/B0BPZJSXCQ?psc=1</t>
         </is>
       </c>
       <c r="K43" s="14" t="inlineStr">
         <is>
-          <t>https://m.media-amazon.com/images/I/51LdyRohTNL._AC_US600_.jpg</t>
+          <t>https://m.media-amazon.com/images/I/41-V4acAJLL._AC_US600_.jpg</t>
         </is>
       </c>
       <c r="L43" s="14" t="inlineStr">
         <is>
-          <t>B0GH6TBJVW</t>
+          <t>B0BPZJSXCQ</t>
         </is>
       </c>
       <c r="M43" s="14" t="inlineStr">
@@ -16998,13 +16906,13 @@
         </is>
       </c>
       <c r="O43" s="15">
-        <v>13837</v>
+        <v>15494</v>
       </c>
       <c r="P43" s="15">
-        <v>28448</v>
+        <v>28351</v>
       </c>
       <c r="Q43" s="16">
-        <v>0.67</v>
+        <v>0.57</v>
       </c>
       <c r="R43" s="17" t="inlineStr">
         <is>
@@ -17013,17 +16921,17 @@
       </c>
       <c r="S43" s="18" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>35</t>
         </is>
       </c>
       <c r="T43" s="15">
-        <v>67</v>
+        <v>50</v>
       </c>
       <c r="U43" s="16">
-        <v>-0.25</v>
+        <v>-0.24</v>
       </c>
       <c r="V43" s="15">
-        <v>4991</v>
+        <v>4318</v>
       </c>
       <c r="W43" s="15"/>
       <c r="X43" s="15"/>
@@ -17031,41 +16939,41 @@
         <v>1</v>
       </c>
       <c r="Z43" s="20">
-        <v>74.49</v>
+        <v>72.53</v>
       </c>
       <c r="AA43"/>
       <c r="AB43"/>
       <c r="AC43" s="2"/>
       <c r="AD43" s="19">
-        <v>85</v>
+        <v>3267</v>
       </c>
       <c r="AE43" s="15">
-        <v>4</v>
+        <v>20</v>
       </c>
       <c r="AF43" s="21">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="AG43" s="22">
-        <v>0.059699999999999996</v>
+        <v>0.4</v>
       </c>
       <c r="AH43" s="20">
-        <v>5.49</v>
+        <v>8.9</v>
       </c>
       <c r="AI43" s="16">
-        <v>0.79</v>
+        <v>0.75</v>
       </c>
       <c r="AJ43"/>
       <c r="AK43" s="13" t="inlineStr">
         <is>
-          <t>2026-04-10</t>
+          <t>2023-03-21</t>
         </is>
       </c>
       <c r="AL43" s="19">
-        <v>142</v>
+        <v>1259</v>
       </c>
       <c r="AM43" s="13" t="inlineStr">
         <is>
-          <t>FBA</t>
+          <t>FBM</t>
         </is>
       </c>
       <c r="AN43" s="13"/>
@@ -17075,35 +16983,39 @@
         <v>10</v>
       </c>
       <c r="AR43" s="19">
-        <v>4</v>
+        <v>19</v>
       </c>
       <c r="AS43" s="14" t="inlineStr">
         <is>
-          <t>BingBon</t>
+          <t>Supermedia online</t>
         </is>
       </c>
       <c r="AT43" s="13" t="inlineStr">
         <is>
-          <t>FBA</t>
+          <t>FBM</t>
         </is>
       </c>
       <c r="AU43" s="13" t="inlineStr">
         <is>
-          <t>CN</t>
+          <t>IT</t>
         </is>
       </c>
       <c r="AV43" s="14" t="inlineStr">
         <is>
-          <t>青岛市 李沧区 山东省 266041 CN</t>
+          <t>Italia 25135 IT</t>
         </is>
       </c>
       <c r="AW43" s="13" t="inlineStr">
         <is>
-          <t>https://www.amazon.it/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A3SC5MLKO5B7LX</t>
+          <t>https://www.amazon.it/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A1PTIZUJDIGRO9</t>
         </is>
       </c>
       <c r="AX43" s="13"/>
-      <c r="AY43" s="13"/>
+      <c r="AY43" s="13" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
       <c r="AZ43" s="13"/>
       <c r="BA43" s="13"/>
       <c r="BB43" s="13"/>
@@ -17121,50 +17033,46 @@
       <c r="BF43" s="13"/>
       <c r="BG43" s="13"/>
       <c r="BH43" s="14"/>
-      <c r="BI43" s="23"/>
+      <c r="BI43" s="23" t="inlineStr">
+        <is>
+          <t>Scelta Amazon</t>
+        </is>
+      </c>
       <c r="BJ43" s="23" t="inlineStr">
         <is>
-          <t>4,7 Kilograms</t>
-        </is>
-      </c>
-      <c r="BK43" s="23" t="inlineStr">
-        <is>
-          <t>4.70 kg</t>
-        </is>
-      </c>
+          <t>3,6 Chilogrammi</t>
+        </is>
+      </c>
+      <c r="BK43" s="23"/>
       <c r="BL43" s="23" t="inlineStr">
         <is>
-          <t>23 x 43 x 32 cm</t>
-        </is>
-      </c>
-      <c r="BM43" s="23" t="inlineStr">
-        <is>
-          <t>23.00 x 43.00 x 32.00 cm</t>
-        </is>
-      </c>
+          <t>27,5P x 22l x 28,5H cm</t>
+        </is>
+      </c>
+      <c r="BM43" s="23"/>
       <c r="BN43" s="23" t="inlineStr">
         <is>
-          <t>4.7 kg</t>
+          <t>4.85 kg</t>
         </is>
       </c>
       <c r="BO43" s="23" t="inlineStr">
         <is>
-          <t>4.70 kg</t>
+          <t>4.85 kg</t>
         </is>
       </c>
       <c r="BP43" s="23" t="inlineStr">
         <is>
-          <t>43.6 x 32.6 x 23.4 cm</t>
+          <t>35.2 x 31 x 30.5 cm</t>
         </is>
       </c>
       <c r="BQ43" s="23" t="inlineStr">
         <is>
-          <t>43.60 x 32.60 x 23.40 cm</t>
+          <t>35.20 x 31.00 x 30.50 cm</t>
         </is>
       </c>
       <c r="BR43" s="13" t="inlineStr">
         <is>
-          <t>标准包裹</t>
+          <t>轻型标准大件</t>
         </is>
       </c>
     </row>
@@ -17175,40 +17083,40 @@
       <c r="B44" s="13"/>
       <c r="C44" s="14" t="inlineStr">
         <is>
-          <t>B0BPZJSXCQ</t>
+          <t>B0CM6TD52F</t>
         </is>
       </c>
       <c r="D44" s="14"/>
       <c r="E44" s="14"/>
       <c r="F44" s="14" t="inlineStr">
         <is>
-          <t>Cecotec</t>
+          <t>LEHMANN POLSKA</t>
         </is>
       </c>
       <c r="G44" s="14" t="inlineStr">
         <is>
-          <t>https://www.amazon.it/Cecotec/b/ref=bl_dp_s_web_19986335031?ie=UTF8&amp;node=19986335031&amp;field-lbr_brands_browse-bin=Cecotec</t>
+          <t>https://www.amazon.it/stores/LEHMANN/page/F8312757-EA08-4E70-8102-256521882264?lp_asin=B0CM6TD52F&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto&amp;bl_grd_status=override</t>
         </is>
       </c>
       <c r="H44" s="14" t="inlineStr">
         <is>
-          <t>Cecotec Aspirapolvere Lava Tappeti Conga 3000 Carpetclean, 3in1:Spruzza, Pulisce e Aspira, 400W, 2 Serbatoi - Acqua Pulita e</t>
+          <t>LEHMANN Ultrawash Aspirapolvere per Lavaggio 4 in 1sAspirapolvere per tappeti e mobili imbottiti | Aspirapolvere senza sacc</t>
         </is>
       </c>
       <c r="I44" s="14"/>
       <c r="J44" s="14" t="inlineStr">
         <is>
-          <t>https://www.amazon.it/dp/B0BPZJSXCQ?psc=1</t>
+          <t>https://www.amazon.it/dp/B0CM6TD52F?psc=1</t>
         </is>
       </c>
       <c r="K44" s="14" t="inlineStr">
         <is>
-          <t>https://m.media-amazon.com/images/I/41-V4acAJLL._AC_US600_.jpg</t>
+          <t>https://m.media-amazon.com/images/I/41zsYT7ETXL._AC_US600_.jpg</t>
         </is>
       </c>
       <c r="L44" s="14" t="inlineStr">
         <is>
-          <t>B0BPZJSXCQ</t>
+          <t>B0CM6TD52F</t>
         </is>
       </c>
       <c r="M44" s="14" t="inlineStr">
@@ -17222,13 +17130,13 @@
         </is>
       </c>
       <c r="O44" s="15">
-        <v>15494</v>
+        <v>29035</v>
       </c>
       <c r="P44" s="15">
-        <v>28351</v>
+        <v>-69553</v>
       </c>
       <c r="Q44" s="16">
-        <v>0.57</v>
+        <v>-3.7</v>
       </c>
       <c r="R44" s="17" t="inlineStr">
         <is>
@@ -17237,17 +17145,17 @@
       </c>
       <c r="S44" s="18" t="inlineStr">
         <is>
-          <t>35</t>
+          <t>47</t>
         </is>
       </c>
       <c r="T44" s="15">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="U44" s="16">
-        <v>-0.24</v>
+        <v>-0.94</v>
       </c>
       <c r="V44" s="15">
-        <v>4318</v>
+        <v>4079</v>
       </c>
       <c r="W44" s="15"/>
       <c r="X44" s="15"/>
@@ -17255,37 +17163,37 @@
         <v>1</v>
       </c>
       <c r="Z44" s="20">
-        <v>72.53</v>
+        <v>79.99</v>
       </c>
       <c r="AA44"/>
       <c r="AB44"/>
       <c r="AC44" s="2"/>
       <c r="AD44" s="19">
-        <v>3267</v>
+        <v>356</v>
       </c>
       <c r="AE44" s="15">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="AF44" s="21">
-        <v>4.3</v>
+        <v>4</v>
       </c>
       <c r="AG44" s="22">
-        <v>0.4</v>
+        <v>0</v>
       </c>
       <c r="AH44" s="20">
-        <v>8.9</v>
+        <v>10.24</v>
       </c>
       <c r="AI44" s="16">
-        <v>0.75</v>
+        <v>0.72</v>
       </c>
       <c r="AJ44"/>
       <c r="AK44" s="13" t="inlineStr">
         <is>
-          <t>2023-03-21</t>
+          <t>2023-11-24</t>
         </is>
       </c>
       <c r="AL44" s="19">
-        <v>1259</v>
+        <v>1010</v>
       </c>
       <c r="AM44" s="13" t="inlineStr">
         <is>
@@ -17299,11 +17207,11 @@
         <v>10</v>
       </c>
       <c r="AR44" s="19">
-        <v>19</v>
+        <v>1</v>
       </c>
       <c r="AS44" s="14" t="inlineStr">
         <is>
-          <t>Supermedia online</t>
+          <t>Lehmann HG</t>
         </is>
       </c>
       <c r="AT44" s="13" t="inlineStr">
@@ -17313,17 +17221,17 @@
       </c>
       <c r="AU44" s="13" t="inlineStr">
         <is>
-          <t>IT</t>
+          <t>PL</t>
         </is>
       </c>
       <c r="AV44" s="14" t="inlineStr">
         <is>
-          <t>Italia 25135 IT</t>
+          <t>Greater Poland 63-100 PL</t>
         </is>
       </c>
       <c r="AW44" s="13" t="inlineStr">
         <is>
-          <t>https://www.amazon.it/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A1PTIZUJDIGRO9</t>
+          <t>https://www.amazon.it/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A2WUCJY3ZYROH</t>
         </is>
       </c>
       <c r="AX44" s="13"/>
@@ -17340,11 +17248,7 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="BD44" s="13" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
+      <c r="BD44" s="13"/>
       <c r="BE44" s="13"/>
       <c r="BF44" s="13"/>
       <c r="BG44" s="13"/>
@@ -17356,34 +17260,38 @@
       </c>
       <c r="BJ44" s="23" t="inlineStr">
         <is>
-          <t>3,6 Chilogrammi</t>
-        </is>
-      </c>
-      <c r="BK44" s="23"/>
+          <t>8,9 Kilograms</t>
+        </is>
+      </c>
+      <c r="BK44" s="23" t="inlineStr">
+        <is>
+          <t>8.90 kg</t>
+        </is>
+      </c>
       <c r="BL44" s="23" t="inlineStr">
         <is>
-          <t>27,5P x 22l x 28,5H cm</t>
+          <t>38L x 33l x 49H cm</t>
         </is>
       </c>
       <c r="BM44" s="23"/>
       <c r="BN44" s="23" t="inlineStr">
         <is>
-          <t>4.85 kg</t>
+          <t>9.18 kg</t>
         </is>
       </c>
       <c r="BO44" s="23" t="inlineStr">
         <is>
-          <t>4.85 kg</t>
+          <t>9.18 kg</t>
         </is>
       </c>
       <c r="BP44" s="23" t="inlineStr">
         <is>
-          <t>35.2 x 31 x 30.5 cm</t>
+          <t>44 x 39 x 36 cm</t>
         </is>
       </c>
       <c r="BQ44" s="23" t="inlineStr">
         <is>
-          <t>35.20 x 31.00 x 30.50 cm</t>
+          <t>44.00 x 39.00 x 36.00 cm</t>
         </is>
       </c>
       <c r="BR44" s="13" t="inlineStr">
@@ -17399,40 +17307,40 @@
       <c r="B45" s="13"/>
       <c r="C45" s="14" t="inlineStr">
         <is>
-          <t>B0CM6TD52F</t>
+          <t>B0GFF7C519</t>
         </is>
       </c>
       <c r="D45" s="14"/>
       <c r="E45" s="14"/>
       <c r="F45" s="14" t="inlineStr">
         <is>
-          <t>LEHMANN POLSKA</t>
+          <t>Akitas</t>
         </is>
       </c>
       <c r="G45" s="14" t="inlineStr">
         <is>
-          <t>https://www.amazon.it/stores/LEHMANN/page/F8312757-EA08-4E70-8102-256521882264?lp_asin=B0CM6TD52F&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto&amp;bl_grd_status=override</t>
+          <t>https://www.amazon.it/stores/Akitas/page/EE82F545-EF96-443C-8B75-30C504BE3C43?lp_asin=B0GFF7C519&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto&amp;bl_grd_status=override</t>
         </is>
       </c>
       <c r="H45" s="14" t="inlineStr">
         <is>
-          <t>LEHMANN Ultrawash Aspirapolvere per Lavaggio 4 in 1sAspirapolvere per tappeti e mobili imbottiti | Aspirapolvere senza sacc</t>
+          <t>Akitas X5 lavatappezzeria per tappeti e imbottiti, con detergente concentrato da 30 ml, doppio serbatoio, autopulizia, legger</t>
         </is>
       </c>
       <c r="I45" s="14"/>
       <c r="J45" s="14" t="inlineStr">
         <is>
-          <t>https://www.amazon.it/dp/B0CM6TD52F?psc=1</t>
+          <t>https://www.amazon.it/dp/B0GFF7C519?psc=1</t>
         </is>
       </c>
       <c r="K45" s="14" t="inlineStr">
         <is>
-          <t>https://m.media-amazon.com/images/I/41zsYT7ETXL._AC_US600_.jpg</t>
+          <t>https://m.media-amazon.com/images/I/41qPnZFK2xL._AC_US600_.jpg</t>
         </is>
       </c>
       <c r="L45" s="14" t="inlineStr">
         <is>
-          <t>B0CM6TD52F</t>
+          <t>B0GFF7C519</t>
         </is>
       </c>
       <c r="M45" s="14" t="inlineStr">
@@ -17446,13 +17354,13 @@
         </is>
       </c>
       <c r="O45" s="15">
-        <v>29035</v>
+        <v>13998</v>
       </c>
       <c r="P45" s="15">
-        <v>-69553</v>
+        <v>12377</v>
       </c>
       <c r="Q45" s="16">
-        <v>-3.7</v>
+        <v>0.67</v>
       </c>
       <c r="R45" s="17" t="inlineStr">
         <is>
@@ -17461,93 +17369,89 @@
       </c>
       <c r="S45" s="18" t="inlineStr">
         <is>
-          <t>47</t>
+          <t>32</t>
         </is>
       </c>
       <c r="T45" s="15">
-        <v>51</v>
-      </c>
-      <c r="U45" s="16">
-        <v>-0.94</v>
-      </c>
+        <v>61</v>
+      </c>
+      <c r="U45" s="16"/>
       <c r="V45" s="15">
-        <v>4079</v>
+        <v>3842</v>
       </c>
       <c r="W45" s="15"/>
       <c r="X45" s="15"/>
       <c r="Y45" s="19">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Z45" s="20">
-        <v>79.99</v>
+        <v>62.99</v>
       </c>
       <c r="AA45"/>
       <c r="AB45"/>
       <c r="AC45" s="2"/>
       <c r="AD45" s="19">
-        <v>356</v>
+        <v>328</v>
       </c>
       <c r="AE45" s="15">
-        <v>0</v>
+        <v>82</v>
       </c>
       <c r="AF45" s="21">
-        <v>4</v>
+        <v>4.5</v>
       </c>
       <c r="AG45" s="22">
         <v>0</v>
       </c>
       <c r="AH45" s="20">
-        <v>10.24</v>
+        <v>5.43</v>
       </c>
       <c r="AI45" s="16">
-        <v>0.72</v>
+        <v>0.76</v>
       </c>
       <c r="AJ45"/>
       <c r="AK45" s="13" t="inlineStr">
         <is>
-          <t>2023-11-24</t>
+          <t>2026-01-22</t>
         </is>
       </c>
       <c r="AL45" s="19">
-        <v>1010</v>
+        <v>221</v>
       </c>
       <c r="AM45" s="13" t="inlineStr">
         <is>
-          <t>FBM</t>
+          <t>FBA</t>
         </is>
       </c>
       <c r="AN45" s="13"/>
       <c r="AO45" s="13"/>
       <c r="AP45"/>
-      <c r="AQ45" s="19">
-        <v>10</v>
-      </c>
+      <c r="AQ45" s="19"/>
       <c r="AR45" s="19">
         <v>1</v>
       </c>
       <c r="AS45" s="14" t="inlineStr">
         <is>
-          <t>Lehmann HG</t>
+          <t>Chelsea Company Limited</t>
         </is>
       </c>
       <c r="AT45" s="13" t="inlineStr">
         <is>
-          <t>FBM</t>
+          <t>FBA</t>
         </is>
       </c>
       <c r="AU45" s="13" t="inlineStr">
         <is>
-          <t>PL</t>
+          <t>CN(HK)</t>
         </is>
       </c>
       <c r="AV45" s="14" t="inlineStr">
         <is>
-          <t>Greater Poland 63-100 PL</t>
+          <t>Tin Hau Hong Kong 852 HK</t>
         </is>
       </c>
       <c r="AW45" s="13" t="inlineStr">
         <is>
-          <t>https://www.amazon.it/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A2WUCJY3ZYROH</t>
+          <t>https://www.amazon.it/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A3ZOAHYWM588P</t>
         </is>
       </c>
       <c r="AX45" s="13"/>
@@ -17564,7 +17468,11 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="BD45" s="13"/>
+      <c r="BD45" s="13" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
       <c r="BE45" s="13"/>
       <c r="BF45" s="13"/>
       <c r="BG45" s="13"/>
@@ -17576,43 +17484,43 @@
       </c>
       <c r="BJ45" s="23" t="inlineStr">
         <is>
-          <t>8,9 Kilograms</t>
+          <t>3,2 Kilograms</t>
         </is>
       </c>
       <c r="BK45" s="23" t="inlineStr">
         <is>
-          <t>8.90 kg</t>
+          <t>3.20 kg</t>
         </is>
       </c>
       <c r="BL45" s="23" t="inlineStr">
         <is>
-          <t>38L x 33l x 49H cm</t>
+          <t>36P x 22l x 28H cm</t>
         </is>
       </c>
       <c r="BM45" s="23"/>
       <c r="BN45" s="23" t="inlineStr">
         <is>
-          <t>9.18 kg</t>
+          <t>3.2 kg</t>
         </is>
       </c>
       <c r="BO45" s="23" t="inlineStr">
         <is>
-          <t>9.18 kg</t>
+          <t>3.20 kg</t>
         </is>
       </c>
       <c r="BP45" s="23" t="inlineStr">
         <is>
-          <t>44 x 39 x 36 cm</t>
+          <t>34.5 x 27.9 x 19.4 cm</t>
         </is>
       </c>
       <c r="BQ45" s="23" t="inlineStr">
         <is>
-          <t>44.00 x 39.00 x 36.00 cm</t>
+          <t>34.50 x 27.90 x 19.40 cm</t>
         </is>
       </c>
       <c r="BR45" s="13" t="inlineStr">
         <is>
-          <t>轻型标准大件</t>
+          <t>标准包裹</t>
         </is>
       </c>
     </row>
@@ -17623,40 +17531,40 @@
       <c r="B46" s="13"/>
       <c r="C46" s="14" t="inlineStr">
         <is>
-          <t>B0GFF7C519</t>
+          <t>B0H3KVMBCH</t>
         </is>
       </c>
       <c r="D46" s="14"/>
       <c r="E46" s="14"/>
       <c r="F46" s="14" t="inlineStr">
         <is>
-          <t>Akitas</t>
+          <t>MELLWIN</t>
         </is>
       </c>
       <c r="G46" s="14" t="inlineStr">
         <is>
-          <t>https://www.amazon.it/stores/Akitas/page/EE82F545-EF96-443C-8B75-30C504BE3C43?lp_asin=B0GFF7C519&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto&amp;bl_grd_status=override</t>
+          <t>https://www.amazon.it/s/ref=bl_dp_s_web_0?ie=UTF8&amp;search-alias=aps&amp;field-keywords=MELLWIN</t>
         </is>
       </c>
       <c r="H46" s="14" t="inlineStr">
         <is>
-          <t>Akitas X5 lavatappezzeria per tappeti e imbottiti, con detergente concentrato da 30 ml, doppio serbatoio, autopulizia, legger</t>
+          <t>MELLWIN lava tappezzeria vapore e riscaldamento,18 kPa,Riscaldamento rapidospulitore tappezzeria da 1250 W Proprietari di a</t>
         </is>
       </c>
       <c r="I46" s="14"/>
       <c r="J46" s="14" t="inlineStr">
         <is>
-          <t>https://www.amazon.it/dp/B0GFF7C519?psc=1</t>
+          <t>https://www.amazon.it/dp/B0H3KVMBCH?psc=1</t>
         </is>
       </c>
       <c r="K46" s="14" t="inlineStr">
         <is>
-          <t>https://m.media-amazon.com/images/I/41qPnZFK2xL._AC_US600_.jpg</t>
+          <t>https://m.media-amazon.com/images/I/41W3WF+EhbL._AC_US600_.jpg</t>
         </is>
       </c>
       <c r="L46" s="14" t="inlineStr">
         <is>
-          <t>B0GFF7C519</t>
+          <t>B0H3KVMBCH</t>
         </is>
       </c>
       <c r="M46" s="14" t="inlineStr">
@@ -17670,13 +17578,13 @@
         </is>
       </c>
       <c r="O46" s="15">
-        <v>13998</v>
+        <v>47443</v>
       </c>
       <c r="P46" s="15">
-        <v>12377</v>
+        <v>48544</v>
       </c>
       <c r="Q46" s="16">
-        <v>0.67</v>
+        <v>0.56</v>
       </c>
       <c r="R46" s="17" t="inlineStr">
         <is>
@@ -17685,53 +17593,51 @@
       </c>
       <c r="S46" s="18" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>54</t>
         </is>
       </c>
       <c r="T46" s="15">
-        <v>61</v>
+        <v>14</v>
       </c>
       <c r="U46" s="16"/>
       <c r="V46" s="15">
-        <v>3842</v>
+        <v>1452</v>
       </c>
       <c r="W46" s="15"/>
       <c r="X46" s="15"/>
       <c r="Y46" s="19">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Z46" s="20">
-        <v>62.99</v>
+        <v>103.74</v>
       </c>
       <c r="AA46"/>
       <c r="AB46"/>
       <c r="AC46" s="2"/>
       <c r="AD46" s="19">
-        <v>328</v>
-      </c>
-      <c r="AE46" s="15">
-        <v>82</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="AE46" s="15"/>
       <c r="AF46" s="21">
-        <v>4.5</v>
+        <v>4</v>
       </c>
       <c r="AG46" s="22">
         <v>0</v>
       </c>
       <c r="AH46" s="20">
-        <v>5.43</v>
+        <v>5.46</v>
       </c>
       <c r="AI46" s="16">
-        <v>0.76</v>
+        <v>0.81</v>
       </c>
       <c r="AJ46"/>
       <c r="AK46" s="13" t="inlineStr">
         <is>
-          <t>2026-01-22</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="AL46" s="19">
-        <v>221</v>
+        <v>23</v>
       </c>
       <c r="AM46" s="13" t="inlineStr">
         <is>
@@ -17741,13 +17647,15 @@
       <c r="AN46" s="13"/>
       <c r="AO46" s="13"/>
       <c r="AP46"/>
-      <c r="AQ46" s="19"/>
+      <c r="AQ46" s="19">
+        <v>8</v>
+      </c>
       <c r="AR46" s="19">
         <v>1</v>
       </c>
       <c r="AS46" s="14" t="inlineStr">
         <is>
-          <t>Chelsea Company Limited</t>
+          <t>EUROAPEX LANDING</t>
         </is>
       </c>
       <c r="AT46" s="13" t="inlineStr">
@@ -17757,25 +17665,21 @@
       </c>
       <c r="AU46" s="13" t="inlineStr">
         <is>
-          <t>CN(HK)</t>
+          <t>PL</t>
         </is>
       </c>
       <c r="AV46" s="14" t="inlineStr">
         <is>
-          <t>Tin Hau Hong Kong 852 HK</t>
+          <t>DOLNOŚLĄSKIE 53-332 PL</t>
         </is>
       </c>
       <c r="AW46" s="13" t="inlineStr">
         <is>
-          <t>https://www.amazon.it/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A3ZOAHYWM588P</t>
+          <t>https://www.amazon.it/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=ABSTVEQNNON26</t>
         </is>
       </c>
       <c r="AX46" s="13"/>
-      <c r="AY46" s="13" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
+      <c r="AY46" s="13"/>
       <c r="AZ46" s="13"/>
       <c r="BA46" s="13"/>
       <c r="BB46" s="13"/>
@@ -17793,45 +17697,41 @@
       <c r="BF46" s="13"/>
       <c r="BG46" s="13"/>
       <c r="BH46" s="14"/>
-      <c r="BI46" s="23" t="inlineStr">
-        <is>
-          <t>Scelta Amazon</t>
-        </is>
-      </c>
+      <c r="BI46" s="23"/>
       <c r="BJ46" s="23" t="inlineStr">
         <is>
-          <t>3,2 Kilograms</t>
-        </is>
-      </c>
-      <c r="BK46" s="23" t="inlineStr">
-        <is>
-          <t>3.20 kg</t>
-        </is>
-      </c>
+          <t>4 Chilogrammi</t>
+        </is>
+      </c>
+      <c r="BK46" s="23"/>
       <c r="BL46" s="23" t="inlineStr">
         <is>
-          <t>36P x 22l x 28H cm</t>
-        </is>
-      </c>
-      <c r="BM46" s="23"/>
+          <t>43 x 19 x 32 cm</t>
+        </is>
+      </c>
+      <c r="BM46" s="23" t="inlineStr">
+        <is>
+          <t>43.00 x 19.00 x 32.00 cm</t>
+        </is>
+      </c>
       <c r="BN46" s="23" t="inlineStr">
         <is>
-          <t>3.2 kg</t>
+          <t>4 kg</t>
         </is>
       </c>
       <c r="BO46" s="23" t="inlineStr">
         <is>
-          <t>3.20 kg</t>
+          <t>4.00 kg</t>
         </is>
       </c>
       <c r="BP46" s="23" t="inlineStr">
         <is>
-          <t>34.5 x 27.9 x 19.4 cm</t>
+          <t>43 x 32 x 19 cm</t>
         </is>
       </c>
       <c r="BQ46" s="23" t="inlineStr">
         <is>
-          <t>34.50 x 27.90 x 19.40 cm</t>
+          <t>43.00 x 32.00 x 19.00 cm</t>
         </is>
       </c>
       <c r="BR46" s="13" t="inlineStr">
@@ -17847,40 +17747,40 @@
       <c r="B47" s="13"/>
       <c r="C47" s="14" t="inlineStr">
         <is>
-          <t>B086Q46MMD</t>
+          <t>B0H4TXR27S</t>
         </is>
       </c>
       <c r="D47" s="14"/>
       <c r="E47" s="14"/>
       <c r="F47" s="14" t="inlineStr">
         <is>
-          <t>STANHOME</t>
+          <t>Redkey</t>
         </is>
       </c>
       <c r="G47" s="14" t="inlineStr">
         <is>
-          <t>https://www.amazon.it/stores/STANHOME/page/CF140807-E9D9-4EE4-98E8-28F83571D17F?lp_asin=B086Q46MMD&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto&amp;bl_grd_status=override</t>
+          <t>https://www.amazon.it/stores/Redkey/page/D0F8E94D-480F-4BD7-ADC2-FEE4358EEB34?lp_asin=B0H4TXR27S&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto</t>
         </is>
       </c>
       <c r="H47" s="14" t="inlineStr">
         <is>
-          <t>STANHOMEsDetergente Smacchiante Tappeti Carpet Cleaner, 500 ML, Pulisce e Smacchia i Tessuti d'Arredamento</t>
+          <t>Redkey Rd-F1 Lavatappeti Lava e Asciuga, 4 in 1 Aspiratore Lava a Vapore con Aspirazione 26000Pa, 1800W Pulizia Profonda per</t>
         </is>
       </c>
       <c r="I47" s="14"/>
       <c r="J47" s="14" t="inlineStr">
         <is>
-          <t>https://www.amazon.it/dp/B086Q46MMD?psc=1</t>
+          <t>https://www.amazon.it/dp/B0H4TXR27S?psc=1</t>
         </is>
       </c>
       <c r="K47" s="14" t="inlineStr">
         <is>
-          <t>https://m.media-amazon.com/images/I/31hUTFxCzpL._AC_US600_.jpg</t>
+          <t>https://m.media-amazon.com/images/I/41f8wwTeaGL._AC_US600_.jpg</t>
         </is>
       </c>
       <c r="L47" s="14" t="inlineStr">
         <is>
-          <t>B086Q46MMD</t>
+          <t>B0H4TXR27S</t>
         </is>
       </c>
       <c r="M47" s="14" t="inlineStr">
@@ -17894,13 +17794,11 @@
         </is>
       </c>
       <c r="O47" s="15">
-        <v>11090</v>
-      </c>
-      <c r="P47" s="15">
-        <v>18109</v>
-      </c>
+        <v>14156</v>
+      </c>
+      <c r="P47" s="15"/>
       <c r="Q47" s="16">
-        <v>0.66</v>
+        <v>0</v>
       </c>
       <c r="R47" s="17" t="inlineStr">
         <is>
@@ -17909,164 +17807,124 @@
       </c>
       <c r="S47" s="18" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>33</t>
         </is>
       </c>
       <c r="T47" s="15">
-        <v>112</v>
-      </c>
-      <c r="U47" s="16">
-        <v>-0.26</v>
-      </c>
+        <v>3</v>
+      </c>
+      <c r="U47" s="16"/>
       <c r="V47" s="15">
-        <v>1680</v>
-      </c>
-      <c r="W47" s="15" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="X47" s="15">
-        <v>750</v>
-      </c>
+        <v>492</v>
+      </c>
+      <c r="W47" s="15"/>
+      <c r="X47" s="15"/>
       <c r="Y47" s="19">
         <v>1</v>
       </c>
       <c r="Z47" s="20">
-        <v>15</v>
+        <v>163.99</v>
       </c>
       <c r="AA47"/>
       <c r="AB47"/>
       <c r="AC47" s="2"/>
-      <c r="AD47" s="19">
-        <v>69</v>
-      </c>
-      <c r="AE47" s="15">
-        <v>3</v>
-      </c>
-      <c r="AF47" s="21">
-        <v>4.4</v>
-      </c>
+      <c r="AD47" s="19"/>
+      <c r="AE47" s="15"/>
+      <c r="AF47" s="21"/>
       <c r="AG47" s="22">
-        <v>0.0268</v>
+        <v>0</v>
       </c>
       <c r="AH47" s="20">
-        <v>3.74</v>
+        <v>9.57</v>
       </c>
       <c r="AI47" s="16">
-        <v>0.6</v>
+        <v>0.79</v>
       </c>
       <c r="AJ47"/>
       <c r="AK47" s="13" t="inlineStr">
         <is>
-          <t>2020-05-09</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="AL47" s="19">
-        <v>2305</v>
+        <v>74</v>
       </c>
       <c r="AM47" s="13" t="inlineStr">
         <is>
-          <t>FBA</t>
+          <t>AMZ</t>
         </is>
       </c>
       <c r="AN47" s="13"/>
       <c r="AO47" s="13"/>
       <c r="AP47"/>
-      <c r="AQ47" s="19">
-        <v>8</v>
-      </c>
+      <c r="AQ47" s="19"/>
       <c r="AR47" s="19">
         <v>1</v>
       </c>
       <c r="AS47" s="14" t="inlineStr">
         <is>
-          <t>Stanhome S.p.A</t>
+          <t>Amazon</t>
         </is>
       </c>
       <c r="AT47" s="13" t="inlineStr">
         <is>
-          <t>FBA</t>
-        </is>
-      </c>
-      <c r="AU47" s="13" t="inlineStr">
-        <is>
-          <t>IT</t>
-        </is>
-      </c>
-      <c r="AV47" s="14" t="inlineStr">
-        <is>
-          <t>ITALIA 25038 IT</t>
-        </is>
-      </c>
-      <c r="AW47" s="13" t="inlineStr">
-        <is>
-          <t>https://www.amazon.it/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A1FKDALFGWQLQF</t>
-        </is>
-      </c>
+          <t>AMZ</t>
+        </is>
+      </c>
+      <c r="AU47" s="13"/>
+      <c r="AV47" s="14"/>
+      <c r="AW47" s="13"/>
       <c r="AX47" s="13"/>
-      <c r="AY47" s="13" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
+      <c r="AY47" s="13"/>
       <c r="AZ47" s="13"/>
       <c r="BA47" s="13"/>
       <c r="BB47" s="13"/>
-      <c r="BC47" s="13"/>
+      <c r="BC47" s="13" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
       <c r="BD47" s="13"/>
       <c r="BE47" s="13"/>
       <c r="BF47" s="13"/>
       <c r="BG47" s="13"/>
       <c r="BH47" s="14"/>
-      <c r="BI47" s="23" t="inlineStr">
-        <is>
-          <t>Scelta Amazon</t>
-        </is>
-      </c>
+      <c r="BI47" s="23"/>
       <c r="BJ47" s="23" t="inlineStr">
         <is>
-          <t>550 grammi</t>
+          <t>6,8 Kilograms</t>
         </is>
       </c>
       <c r="BK47" s="23" t="inlineStr">
         <is>
-          <t>550.00 g</t>
-        </is>
-      </c>
-      <c r="BL47" s="23" t="inlineStr">
-        <is>
-          <t>6,7 x 24 x 6,7 cm</t>
-        </is>
-      </c>
-      <c r="BM47" s="23" t="inlineStr">
-        <is>
-          <t>6.70 x 24.00 x 6.70 cm</t>
-        </is>
-      </c>
+          <t>6.80 kg</t>
+        </is>
+      </c>
+      <c r="BL47" s="23"/>
+      <c r="BM47" s="23"/>
       <c r="BN47" s="23" t="inlineStr">
         <is>
-          <t>550 g</t>
+          <t>6.8 kg</t>
         </is>
       </c>
       <c r="BO47" s="23" t="inlineStr">
         <is>
-          <t>550.00 g</t>
+          <t>6.80 kg</t>
         </is>
       </c>
       <c r="BP47" s="23" t="inlineStr">
         <is>
-          <t>23.7 x 6.1 x 6 cm</t>
+          <t>37 x 35 x 35 cm</t>
         </is>
       </c>
       <c r="BQ47" s="23" t="inlineStr">
         <is>
-          <t>23.70 x 6.10 x 6.00 cm</t>
+          <t>37.00 x 35.00 x 35.00 cm</t>
         </is>
       </c>
       <c r="BR47" s="13" t="inlineStr">
         <is>
-          <t>超大号信封</t>
+          <t>轻型标准大件</t>
         </is>
       </c>
     </row>
@@ -18077,40 +17935,40 @@
       <c r="B48" s="13"/>
       <c r="C48" s="14" t="inlineStr">
         <is>
-          <t>B0H3KVMBCH</t>
+          <t>B0H97LW9DL</t>
         </is>
       </c>
       <c r="D48" s="14"/>
       <c r="E48" s="14"/>
       <c r="F48" s="14" t="inlineStr">
         <is>
-          <t>MELLWIN</t>
+          <t>PUREBEAR</t>
         </is>
       </c>
       <c r="G48" s="14" t="inlineStr">
         <is>
-          <t>https://www.amazon.it/s/ref=bl_dp_s_web_0?ie=UTF8&amp;search-alias=aps&amp;field-keywords=MELLWIN</t>
+          <t>https://www.amazon.it/stores/Rispostaimmediatain24ore/page/DC11DA78-3928-4F1D-8E2F-8AD84D6FF0A2?lp_asin=B0H97LW9DL&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto&amp;bl_grd_status=override</t>
         </is>
       </c>
       <c r="H48" s="14" t="inlineStr">
         <is>
-          <t>MELLWIN lava tappezzeria vapore e riscaldamento,18 kPa,Riscaldamento rapidospulitore tappezzeria da 1250 W Proprietari di a</t>
+          <t>PUREBEAR Pulitore Tappezzeria, Lavatappeti Divani Lava (Bianco)</t>
         </is>
       </c>
       <c r="I48" s="14"/>
       <c r="J48" s="14" t="inlineStr">
         <is>
-          <t>https://www.amazon.it/dp/B0H3KVMBCH?psc=1</t>
+          <t>https://www.amazon.it/dp/B0H97LW9DL?psc=1</t>
         </is>
       </c>
       <c r="K48" s="14" t="inlineStr">
         <is>
-          <t>https://m.media-amazon.com/images/I/41W3WF+EhbL._AC_US600_.jpg</t>
+          <t>https://images-na.ssl-images-amazon.com/images/I/51LnggCx6eL._AC_US600_.jpg</t>
         </is>
       </c>
       <c r="L48" s="14" t="inlineStr">
         <is>
-          <t>B0H3KVMBCH</t>
+          <t>B0H97LW9DL</t>
         </is>
       </c>
       <c r="M48" s="14" t="inlineStr">
@@ -18124,13 +17982,11 @@
         </is>
       </c>
       <c r="O48" s="15">
-        <v>47443</v>
-      </c>
-      <c r="P48" s="15">
-        <v>48544</v>
-      </c>
+        <v>34874</v>
+      </c>
+      <c r="P48" s="15"/>
       <c r="Q48" s="16">
-        <v>0.56</v>
+        <v>0</v>
       </c>
       <c r="R48" s="17" t="inlineStr">
         <is>
@@ -18139,15 +17995,15 @@
       </c>
       <c r="S48" s="18" t="inlineStr">
         <is>
-          <t>54</t>
+          <t>50</t>
         </is>
       </c>
       <c r="T48" s="15">
-        <v>14</v>
+        <v>2</v>
       </c>
       <c r="U48" s="16"/>
       <c r="V48" s="15">
-        <v>1452</v>
+        <v>280</v>
       </c>
       <c r="W48" s="15"/>
       <c r="X48" s="15"/>
@@ -18155,39 +18011,41 @@
         <v>1</v>
       </c>
       <c r="Z48" s="20">
-        <v>103.74</v>
+        <v>139.99</v>
       </c>
       <c r="AA48"/>
       <c r="AB48"/>
       <c r="AC48" s="2"/>
       <c r="AD48" s="19">
-        <v>1</v>
-      </c>
-      <c r="AE48" s="15"/>
+        <v>20</v>
+      </c>
+      <c r="AE48" s="15">
+        <v>0</v>
+      </c>
       <c r="AF48" s="21">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AG48" s="22">
         <v>0</v>
       </c>
       <c r="AH48" s="20">
-        <v>5.46</v>
+        <v>8.9</v>
       </c>
       <c r="AI48" s="16">
-        <v>0.81</v>
+        <v>0.79</v>
       </c>
       <c r="AJ48"/>
       <c r="AK48" s="13" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-22</t>
         </is>
       </c>
       <c r="AL48" s="19">
-        <v>23</v>
+        <v>8</v>
       </c>
       <c r="AM48" s="13" t="inlineStr">
         <is>
-          <t>FBA</t>
+          <t>NA</t>
         </is>
       </c>
       <c r="AN48" s="13"/>
@@ -18201,27 +18059,27 @@
       </c>
       <c r="AS48" s="14" t="inlineStr">
         <is>
-          <t>EUROAPEX LANDING</t>
+          <t>MengfanchaoMLw</t>
         </is>
       </c>
       <c r="AT48" s="13" t="inlineStr">
         <is>
-          <t>FBA</t>
+          <t>NA</t>
         </is>
       </c>
       <c r="AU48" s="13" t="inlineStr">
         <is>
-          <t>PL</t>
+          <t>CN</t>
         </is>
       </c>
       <c r="AV48" s="14" t="inlineStr">
         <is>
-          <t>DOLNOŚLĄSKIE 53-332 PL</t>
+          <t>huanggangshi hubeisheng 438000 CN</t>
         </is>
       </c>
       <c r="AW48" s="13" t="inlineStr">
         <is>
-          <t>https://www.amazon.it/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=ABSTVEQNNON26</t>
+          <t>https://www.amazon.it/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A1SGZEKAW8X162</t>
         </is>
       </c>
       <c r="AX48" s="13"/>
@@ -18246,43 +18104,39 @@
       <c r="BI48" s="23"/>
       <c r="BJ48" s="23" t="inlineStr">
         <is>
-          <t>4 Chilogrammi</t>
-        </is>
-      </c>
-      <c r="BK48" s="23"/>
-      <c r="BL48" s="23" t="inlineStr">
-        <is>
-          <t>43 x 19 x 32 cm</t>
-        </is>
-      </c>
-      <c r="BM48" s="23" t="inlineStr">
-        <is>
-          <t>43.00 x 19.00 x 32.00 cm</t>
-        </is>
-      </c>
+          <t>4,5 Kilograms</t>
+        </is>
+      </c>
+      <c r="BK48" s="23" t="inlineStr">
+        <is>
+          <t>4.50 kg</t>
+        </is>
+      </c>
+      <c r="BL48" s="23"/>
+      <c r="BM48" s="23"/>
       <c r="BN48" s="23" t="inlineStr">
         <is>
-          <t>4 kg</t>
+          <t>4.5 kg</t>
         </is>
       </c>
       <c r="BO48" s="23" t="inlineStr">
         <is>
-          <t>4.00 kg</t>
+          <t>4.50 kg</t>
         </is>
       </c>
       <c r="BP48" s="23" t="inlineStr">
         <is>
-          <t>43 x 32 x 19 cm</t>
+          <t>53.5 x 32 x 18 cm</t>
         </is>
       </c>
       <c r="BQ48" s="23" t="inlineStr">
         <is>
-          <t>43.00 x 32.00 x 19.00 cm</t>
+          <t>53.50 x 32.00 x 18.00 cm</t>
         </is>
       </c>
       <c r="BR48" s="13" t="inlineStr">
         <is>
-          <t>标准包裹</t>
+          <t>轻型标准大件</t>
         </is>
       </c>
     </row>
@@ -18293,130 +18147,80 @@
       <c r="B49" s="13"/>
       <c r="C49" s="14" t="inlineStr">
         <is>
-          <t>B0H4TXR27S</t>
+          <t>B08KXVXC82</t>
         </is>
       </c>
       <c r="D49" s="14"/>
       <c r="E49" s="14"/>
-      <c r="F49" s="14" t="inlineStr">
-        <is>
-          <t>Redkey</t>
-        </is>
-      </c>
+      <c r="F49" s="14"/>
       <c r="G49" s="14" t="inlineStr">
         <is>
-          <t>https://www.amazon.it/stores/Redkey/page/D0F8E94D-480F-4BD7-ADC2-FEE4358EEB34?lp_asin=B0H4TXR27S&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto</t>
+          <t>https://www.amazon.itundefined</t>
         </is>
       </c>
       <c r="H49" s="14" t="inlineStr">
         <is>
-          <t>Redkey Rd-F1 Lavatappeti Lava e Asciuga, 4 in 1 Aspiratore Lava a Vapore con Aspirazione 26000Pa, 1800W Pulizia Profonda per</t>
+          <t>MEDION Pulitore per tappezzeria lava aspiraliquidi (Aspiratore a umido per tappezzeria, tappeti e sedili auto, serbatoio acqu</t>
         </is>
       </c>
       <c r="I49" s="14"/>
       <c r="J49" s="14" t="inlineStr">
         <is>
-          <t>https://www.amazon.it/dp/B0H4TXR27S?psc=1</t>
+          <t>https://www.amazon.it/dp/B08KXVXC82?psc=1</t>
         </is>
       </c>
       <c r="K49" s="14" t="inlineStr">
         <is>
-          <t>https://m.media-amazon.com/images/I/41f8wwTeaGL._AC_US600_.jpg</t>
+          <t>https://images-eu.ssl-images-amazon.com/images/I/71A5BQeECwL._AC_UL300_SR300,200_.jpg</t>
         </is>
       </c>
       <c r="L49" s="14" t="inlineStr">
         <is>
-          <t>B0H4TXR27S</t>
-        </is>
-      </c>
-      <c r="M49" s="14" t="inlineStr">
-        <is>
-          <t>Casa e cucina:Aspirapolvere e pulizia di pavimenti e finestre:Lavatappeti</t>
-        </is>
-      </c>
-      <c r="N49" s="14" t="inlineStr">
-        <is>
-          <t>Visualizza i Top 100 nella categoria Casa e c</t>
-        </is>
-      </c>
-      <c r="O49" s="15">
-        <v>14156</v>
-      </c>
+          <t>B08KXVXC82</t>
+        </is>
+      </c>
+      <c r="M49" s="14"/>
+      <c r="N49" s="14"/>
+      <c r="O49" s="15"/>
       <c r="P49" s="15"/>
-      <c r="Q49" s="16">
-        <v>0</v>
-      </c>
-      <c r="R49" s="17" t="inlineStr">
-        <is>
-          <t>Lavatappeti</t>
-        </is>
-      </c>
-      <c r="S49" s="18" t="inlineStr">
-        <is>
-          <t>33</t>
-        </is>
-      </c>
-      <c r="T49" s="15">
-        <v>3</v>
-      </c>
+      <c r="Q49" s="16"/>
+      <c r="R49" s="17"/>
+      <c r="S49" s="18"/>
+      <c r="T49" s="15"/>
       <c r="U49" s="16"/>
-      <c r="V49" s="15">
-        <v>492</v>
-      </c>
+      <c r="V49" s="15"/>
       <c r="W49" s="15"/>
       <c r="X49" s="15"/>
-      <c r="Y49" s="19">
-        <v>1</v>
-      </c>
-      <c r="Z49" s="20">
-        <v>163.99</v>
-      </c>
+      <c r="Y49" s="19"/>
+      <c r="Z49" s="20"/>
       <c r="AA49"/>
       <c r="AB49"/>
       <c r="AC49" s="2"/>
-      <c r="AD49" s="19"/>
+      <c r="AD49" s="19">
+        <v>68</v>
+      </c>
       <c r="AE49" s="15"/>
-      <c r="AF49" s="21"/>
+      <c r="AF49" s="21">
+        <v>4.6</v>
+      </c>
       <c r="AG49" s="22">
         <v>0</v>
       </c>
-      <c r="AH49" s="20">
-        <v>9.57</v>
-      </c>
+      <c r="AH49" s="20"/>
       <c r="AI49" s="16">
-        <v>0.79</v>
+        <v>0</v>
       </c>
       <c r="AJ49"/>
-      <c r="AK49" s="13" t="inlineStr">
-        <is>
-          <t>2026-06-17</t>
-        </is>
-      </c>
-      <c r="AL49" s="19">
-        <v>74</v>
-      </c>
-      <c r="AM49" s="13" t="inlineStr">
-        <is>
-          <t>AMZ</t>
-        </is>
-      </c>
+      <c r="AK49" s="13"/>
+      <c r="AL49" s="19"/>
+      <c r="AM49" s="13"/>
       <c r="AN49" s="13"/>
       <c r="AO49" s="13"/>
       <c r="AP49"/>
       <c r="AQ49" s="19"/>
-      <c r="AR49" s="19">
-        <v>1</v>
-      </c>
-      <c r="AS49" s="14" t="inlineStr">
-        <is>
-          <t>Amazon</t>
-        </is>
-      </c>
-      <c r="AT49" s="13" t="inlineStr">
-        <is>
-          <t>AMZ</t>
-        </is>
-      </c>
+      <c r="AR49" s="19"/>
+      <c r="AS49" s="14"/>
+      <c r="AT49" s="13"/>
       <c r="AU49" s="13"/>
       <c r="AV49" s="14"/>
       <c r="AW49" s="13"/>
@@ -18425,372 +18229,22 @@
       <c r="AZ49" s="13"/>
       <c r="BA49" s="13"/>
       <c r="BB49" s="13"/>
-      <c r="BC49" s="13" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
+      <c r="BC49" s="13"/>
       <c r="BD49" s="13"/>
       <c r="BE49" s="13"/>
       <c r="BF49" s="13"/>
       <c r="BG49" s="13"/>
       <c r="BH49" s="14"/>
       <c r="BI49" s="23"/>
-      <c r="BJ49" s="23" t="inlineStr">
-        <is>
-          <t>6,8 Kilograms</t>
-        </is>
-      </c>
-      <c r="BK49" s="23" t="inlineStr">
-        <is>
-          <t>6.80 kg</t>
-        </is>
-      </c>
+      <c r="BJ49" s="23"/>
+      <c r="BK49" s="23"/>
       <c r="BL49" s="23"/>
       <c r="BM49" s="23"/>
-      <c r="BN49" s="23" t="inlineStr">
-        <is>
-          <t>6.8 kg</t>
-        </is>
-      </c>
-      <c r="BO49" s="23" t="inlineStr">
-        <is>
-          <t>6.80 kg</t>
-        </is>
-      </c>
-      <c r="BP49" s="23" t="inlineStr">
-        <is>
-          <t>37 x 35 x 35 cm</t>
-        </is>
-      </c>
-      <c r="BQ49" s="23" t="inlineStr">
-        <is>
-          <t>37.00 x 35.00 x 35.00 cm</t>
-        </is>
-      </c>
-      <c r="BR49" s="13" t="inlineStr">
-        <is>
-          <t>轻型标准大件</t>
-        </is>
-      </c>
-    </row>
-    <row r="50" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A50" s="13">
-        <v>49</v>
-      </c>
-      <c r="B50" s="13"/>
-      <c r="C50" s="14" t="inlineStr">
-        <is>
-          <t>B0H97LW9DL</t>
-        </is>
-      </c>
-      <c r="D50" s="14"/>
-      <c r="E50" s="14"/>
-      <c r="F50" s="14" t="inlineStr">
-        <is>
-          <t>PUREBEAR</t>
-        </is>
-      </c>
-      <c r="G50" s="14" t="inlineStr">
-        <is>
-          <t>https://www.amazon.it/stores/Rispostaimmediatain24ore/page/DC11DA78-3928-4F1D-8E2F-8AD84D6FF0A2?lp_asin=B0H97LW9DL&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto&amp;bl_grd_status=override</t>
-        </is>
-      </c>
-      <c r="H50" s="14" t="inlineStr">
-        <is>
-          <t>PUREBEAR Pulitore Tappezzeria, Lavatappeti Divani Lava (Bianco)</t>
-        </is>
-      </c>
-      <c r="I50" s="14"/>
-      <c r="J50" s="14" t="inlineStr">
-        <is>
-          <t>https://www.amazon.it/dp/B0H97LW9DL?psc=1</t>
-        </is>
-      </c>
-      <c r="K50" s="14" t="inlineStr">
-        <is>
-          <t>https://images-na.ssl-images-amazon.com/images/I/51LnggCx6eL._AC_US600_.jpg</t>
-        </is>
-      </c>
-      <c r="L50" s="14" t="inlineStr">
-        <is>
-          <t>B0H97LW9DL</t>
-        </is>
-      </c>
-      <c r="M50" s="14" t="inlineStr">
-        <is>
-          <t>Casa e cucina:Aspirapolvere e pulizia di pavimenti e finestre:Lavatappeti</t>
-        </is>
-      </c>
-      <c r="N50" s="14" t="inlineStr">
-        <is>
-          <t>Visualizza i Top 100 nella categoria Casa e c</t>
-        </is>
-      </c>
-      <c r="O50" s="15">
-        <v>34874</v>
-      </c>
-      <c r="P50" s="15"/>
-      <c r="Q50" s="16">
-        <v>0</v>
-      </c>
-      <c r="R50" s="17" t="inlineStr">
-        <is>
-          <t>Lavatappeti</t>
-        </is>
-      </c>
-      <c r="S50" s="18" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="T50" s="15">
-        <v>2</v>
-      </c>
-      <c r="U50" s="16"/>
-      <c r="V50" s="15">
-        <v>280</v>
-      </c>
-      <c r="W50" s="15"/>
-      <c r="X50" s="15"/>
-      <c r="Y50" s="19">
-        <v>1</v>
-      </c>
-      <c r="Z50" s="20">
-        <v>139.99</v>
-      </c>
-      <c r="AA50"/>
-      <c r="AB50"/>
-      <c r="AC50" s="2"/>
-      <c r="AD50" s="19">
-        <v>20</v>
-      </c>
-      <c r="AE50" s="15">
-        <v>0</v>
-      </c>
-      <c r="AF50" s="21">
-        <v>5</v>
-      </c>
-      <c r="AG50" s="22">
-        <v>0</v>
-      </c>
-      <c r="AH50" s="20">
-        <v>8.9</v>
-      </c>
-      <c r="AI50" s="16">
-        <v>0.79</v>
-      </c>
-      <c r="AJ50"/>
-      <c r="AK50" s="13" t="inlineStr">
-        <is>
-          <t>2026-08-22</t>
-        </is>
-      </c>
-      <c r="AL50" s="19">
-        <v>8</v>
-      </c>
-      <c r="AM50" s="13" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
-      </c>
-      <c r="AN50" s="13"/>
-      <c r="AO50" s="13"/>
-      <c r="AP50"/>
-      <c r="AQ50" s="19">
-        <v>8</v>
-      </c>
-      <c r="AR50" s="19">
-        <v>1</v>
-      </c>
-      <c r="AS50" s="14" t="inlineStr">
-        <is>
-          <t>MengfanchaoMLw</t>
-        </is>
-      </c>
-      <c r="AT50" s="13" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
-      </c>
-      <c r="AU50" s="13" t="inlineStr">
-        <is>
-          <t>CN</t>
-        </is>
-      </c>
-      <c r="AV50" s="14" t="inlineStr">
-        <is>
-          <t>huanggangshi hubeisheng 438000 CN</t>
-        </is>
-      </c>
-      <c r="AW50" s="13" t="inlineStr">
-        <is>
-          <t>https://www.amazon.it/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A1SGZEKAW8X162</t>
-        </is>
-      </c>
-      <c r="AX50" s="13"/>
-      <c r="AY50" s="13"/>
-      <c r="AZ50" s="13"/>
-      <c r="BA50" s="13"/>
-      <c r="BB50" s="13"/>
-      <c r="BC50" s="13" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="BD50" s="13" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="BE50" s="13"/>
-      <c r="BF50" s="13"/>
-      <c r="BG50" s="13"/>
-      <c r="BH50" s="14"/>
-      <c r="BI50" s="23"/>
-      <c r="BJ50" s="23" t="inlineStr">
-        <is>
-          <t>4,5 Kilograms</t>
-        </is>
-      </c>
-      <c r="BK50" s="23" t="inlineStr">
-        <is>
-          <t>4.50 kg</t>
-        </is>
-      </c>
-      <c r="BL50" s="23"/>
-      <c r="BM50" s="23"/>
-      <c r="BN50" s="23" t="inlineStr">
-        <is>
-          <t>4.5 kg</t>
-        </is>
-      </c>
-      <c r="BO50" s="23" t="inlineStr">
-        <is>
-          <t>4.50 kg</t>
-        </is>
-      </c>
-      <c r="BP50" s="23" t="inlineStr">
-        <is>
-          <t>53.5 x 32 x 18 cm</t>
-        </is>
-      </c>
-      <c r="BQ50" s="23" t="inlineStr">
-        <is>
-          <t>53.50 x 32.00 x 18.00 cm</t>
-        </is>
-      </c>
-      <c r="BR50" s="13" t="inlineStr">
-        <is>
-          <t>轻型标准大件</t>
-        </is>
-      </c>
-    </row>
-    <row r="51" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A51" s="13">
-        <v>50</v>
-      </c>
-      <c r="B51" s="13"/>
-      <c r="C51" s="14" t="inlineStr">
-        <is>
-          <t>B08KXVXC82</t>
-        </is>
-      </c>
-      <c r="D51" s="14"/>
-      <c r="E51" s="14"/>
-      <c r="F51" s="14"/>
-      <c r="G51" s="14" t="inlineStr">
-        <is>
-          <t>https://www.amazon.itundefined</t>
-        </is>
-      </c>
-      <c r="H51" s="14" t="inlineStr">
-        <is>
-          <t>MEDION Pulitore per tappezzeria lava aspiraliquidi (Aspiratore a umido per tappezzeria, tappeti e sedili auto, serbatoio acqu</t>
-        </is>
-      </c>
-      <c r="I51" s="14"/>
-      <c r="J51" s="14" t="inlineStr">
-        <is>
-          <t>https://www.amazon.it/dp/B08KXVXC82?psc=1</t>
-        </is>
-      </c>
-      <c r="K51" s="14" t="inlineStr">
-        <is>
-          <t>https://images-eu.ssl-images-amazon.com/images/I/71A5BQeECwL._AC_UL300_SR300,200_.jpg</t>
-        </is>
-      </c>
-      <c r="L51" s="14" t="inlineStr">
-        <is>
-          <t>B08KXVXC82</t>
-        </is>
-      </c>
-      <c r="M51" s="14"/>
-      <c r="N51" s="14"/>
-      <c r="O51" s="15"/>
-      <c r="P51" s="15"/>
-      <c r="Q51" s="16"/>
-      <c r="R51" s="17"/>
-      <c r="S51" s="18"/>
-      <c r="T51" s="15"/>
-      <c r="U51" s="16"/>
-      <c r="V51" s="15"/>
-      <c r="W51" s="15"/>
-      <c r="X51" s="15"/>
-      <c r="Y51" s="19"/>
-      <c r="Z51" s="20"/>
-      <c r="AA51"/>
-      <c r="AB51"/>
-      <c r="AC51" s="2"/>
-      <c r="AD51" s="19">
-        <v>68</v>
-      </c>
-      <c r="AE51" s="15"/>
-      <c r="AF51" s="21">
-        <v>4.6</v>
-      </c>
-      <c r="AG51" s="22">
-        <v>0</v>
-      </c>
-      <c r="AH51" s="20"/>
-      <c r="AI51" s="16">
-        <v>0</v>
-      </c>
-      <c r="AJ51"/>
-      <c r="AK51" s="13"/>
-      <c r="AL51" s="19"/>
-      <c r="AM51" s="13"/>
-      <c r="AN51" s="13"/>
-      <c r="AO51" s="13"/>
-      <c r="AP51"/>
-      <c r="AQ51" s="19"/>
-      <c r="AR51" s="19"/>
-      <c r="AS51" s="14"/>
-      <c r="AT51" s="13"/>
-      <c r="AU51" s="13"/>
-      <c r="AV51" s="14"/>
-      <c r="AW51" s="13"/>
-      <c r="AX51" s="13"/>
-      <c r="AY51" s="13"/>
-      <c r="AZ51" s="13"/>
-      <c r="BA51" s="13"/>
-      <c r="BB51" s="13"/>
-      <c r="BC51" s="13"/>
-      <c r="BD51" s="13"/>
-      <c r="BE51" s="13"/>
-      <c r="BF51" s="13"/>
-      <c r="BG51" s="13"/>
-      <c r="BH51" s="14"/>
-      <c r="BI51" s="23"/>
-      <c r="BJ51" s="23"/>
-      <c r="BK51" s="23"/>
-      <c r="BL51" s="23"/>
-      <c r="BM51" s="23"/>
-      <c r="BN51" s="23"/>
-      <c r="BO51" s="23"/>
-      <c r="BP51" s="23"/>
-      <c r="BQ51" s="23"/>
-      <c r="BR51" s="13"/>
+      <c r="BN49" s="23"/>
+      <c r="BO49" s="23"/>
+      <c r="BP49" s="23"/>
+      <c r="BQ49" s="23"/>
+      <c r="BR49" s="13"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -19028,150 +18482,135 @@
     <hyperlink ref="L33" r:id="rId230" tooltip="https://www.amazon.it/dp/B0DBLD211L"/>
     <hyperlink ref="M33" r:id="rId231" tooltip="https://www.amazon.it/b?node=733005031"/>
     <hyperlink ref="N33" r:id="rId232"/>
-    <hyperlink ref="C34" r:id="rId233" tooltip="https://www.amazon.it/dp/B0753NXDPR"/>
-    <hyperlink ref="G34" r:id="rId234" tooltip="https://www.amazon.it/stores/BISSELL/page/EDA95B6C-7064-466B-BACA-347C73A9A423?lp_asin=B0753NXDPR&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto"/>
-    <hyperlink ref="J34" r:id="rId235" tooltip="https://www.amazon.it/dp/B0753NXDPR?psc=1"/>
-    <hyperlink ref="K34" r:id="rId236" tooltip="https://m.media-amazon.com/images/I/31BhvLWbbNL._AC_US600_.jpg"/>
-    <hyperlink ref="L34" r:id="rId237" tooltip="https://www.amazon.it/dp/B0753NXDPR"/>
-    <hyperlink ref="M34" r:id="rId238" tooltip="https://www.amazon.it/b?node=28122080031"/>
+    <hyperlink ref="C34" r:id="rId233" tooltip="https://www.amazon.it/dp/B0H3LCDNGF"/>
+    <hyperlink ref="G34" r:id="rId234" tooltip="https://www.amazon.it/stores/LEHMANN/page/F8312757-EA08-4E70-8102-256521882264?lp_asin=B0H3LCDNGF&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto&amp;bl_grd_status=override"/>
+    <hyperlink ref="J34" r:id="rId235" tooltip="https://www.amazon.it/dp/B0H3LCDNGF?psc=1"/>
+    <hyperlink ref="K34" r:id="rId236" tooltip="https://m.media-amazon.com/images/I/41Md9nniqDL._AC_US600_.jpg"/>
+    <hyperlink ref="L34" r:id="rId237" tooltip="https://www.amazon.it/dp/B0H3LCDNGF"/>
+    <hyperlink ref="M34" r:id="rId238" tooltip="https://www.amazon.it/b?node=733005031"/>
     <hyperlink ref="N34" r:id="rId239"/>
-    <hyperlink ref="C35" r:id="rId240" tooltip="https://www.amazon.it/dp/B0H3LCDNGF"/>
-    <hyperlink ref="G35" r:id="rId241" tooltip="https://www.amazon.it/stores/LEHMANN/page/F8312757-EA08-4E70-8102-256521882264?lp_asin=B0H3LCDNGF&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto&amp;bl_grd_status=override"/>
-    <hyperlink ref="J35" r:id="rId242" tooltip="https://www.amazon.it/dp/B0H3LCDNGF?psc=1"/>
-    <hyperlink ref="K35" r:id="rId243" tooltip="https://m.media-amazon.com/images/I/41Md9nniqDL._AC_US600_.jpg"/>
-    <hyperlink ref="L35" r:id="rId244" tooltip="https://www.amazon.it/dp/B0H3LCDNGF"/>
-    <hyperlink ref="M35" r:id="rId245" tooltip="https://www.amazon.it/b?node=733005031"/>
-    <hyperlink ref="N35" r:id="rId246"/>
-    <hyperlink ref="AW35" r:id="rId247" tooltip="https://www.amazon.it/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A2WUCJY3ZYROH"/>
-    <hyperlink ref="C36" r:id="rId248" tooltip="https://www.amazon.it/dp/B0GLNFSYRW"/>
-    <hyperlink ref="G36" r:id="rId249" tooltip="https://www.amazon.it/s/ref=bl_dp_s_web_0?ie=UTF8&amp;search-alias=aps&amp;field-keywords=Vozascly"/>
-    <hyperlink ref="J36" r:id="rId250" tooltip="https://www.amazon.it/dp/B0GLNFSYRW?psc=1"/>
-    <hyperlink ref="K36" r:id="rId251" tooltip="https://m.media-amazon.com/images/I/41zOwfkwiCL._AC_US600_.jpg"/>
-    <hyperlink ref="L36" r:id="rId252" tooltip="https://www.amazon.it/dp/B0GLNFSYRW"/>
-    <hyperlink ref="M36" r:id="rId253" tooltip="https://www.amazon.it/b?node=733005031"/>
-    <hyperlink ref="N36" r:id="rId254"/>
-    <hyperlink ref="AW36" r:id="rId255" tooltip="https://www.amazon.it/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=AEBC603LGC1S2"/>
-    <hyperlink ref="C37" r:id="rId256" tooltip="https://www.amazon.it/dp/B0BSHCQQ4W"/>
-    <hyperlink ref="G37" r:id="rId257" tooltip="https://www.amazon.it/stores/HKoenig/page/978AEC1C-8AF0-4DD0-AECD-D6014C0418DD?lp_asin=B0BSHCQQ4W&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto&amp;bl_grd_status=override"/>
-    <hyperlink ref="J37" r:id="rId258" tooltip="https://www.amazon.it/dp/B0BSHCQQ4W?psc=1"/>
-    <hyperlink ref="K37" r:id="rId259" tooltip="https://m.media-amazon.com/images/I/41EDgJP8-JL._AC_US600_.jpg"/>
-    <hyperlink ref="L37" r:id="rId260" tooltip="https://www.amazon.it/dp/B0BSHCQQ4W"/>
-    <hyperlink ref="M37" r:id="rId261" tooltip="https://www.amazon.it/b?node=733005031"/>
-    <hyperlink ref="N37" r:id="rId262"/>
-    <hyperlink ref="AW37" r:id="rId263" tooltip="https://www.amazon.it/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A2J1ZXSJG29176"/>
-    <hyperlink ref="C38" r:id="rId264" tooltip="https://www.amazon.it/dp/B0FJFDG5PY"/>
-    <hyperlink ref="G38" r:id="rId265" tooltip="https://www.amazon.it/stores/Akitas/page/EE82F545-EF96-443C-8B75-30C504BE3C43?lp_asin=B0FJFDG5PY&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto&amp;bl_grd_status=override"/>
-    <hyperlink ref="J38" r:id="rId266" tooltip="https://www.amazon.it/dp/B0FJFDG5PY?psc=1"/>
-    <hyperlink ref="K38" r:id="rId267" tooltip="https://m.media-amazon.com/images/I/41MJX3SSe4L._AC_US600_.jpg"/>
-    <hyperlink ref="L38" r:id="rId268" tooltip="https://www.amazon.it/dp/B0FJFDG5PY"/>
-    <hyperlink ref="M38" r:id="rId269" tooltip="https://www.amazon.it/b?node=733005031"/>
-    <hyperlink ref="N38" r:id="rId270"/>
-    <hyperlink ref="AW38" r:id="rId271" tooltip="https://www.amazon.it/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A3ZOAHYWM588P"/>
-    <hyperlink ref="C39" r:id="rId272" tooltip="https://www.amazon.it/dp/B0BTHFNNH1"/>
-    <hyperlink ref="G39" r:id="rId273" tooltip="https://www.amazon.it/stores/VACMASTER/page/F372FF16-5498-423D-9923-A4EFB43DC86B?lp_asin=B0BTHFNNH1&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto"/>
-    <hyperlink ref="J39" r:id="rId274" tooltip="https://www.amazon.it/dp/B0BTHFNNH1?psc=1"/>
-    <hyperlink ref="K39" r:id="rId275" tooltip="https://images-na.ssl-images-amazon.com/images/I/81ygbNkGjPL._AC_US600_.jpg"/>
-    <hyperlink ref="L39" r:id="rId276" tooltip="https://www.amazon.it/dp/B0BTHFNNH1"/>
+    <hyperlink ref="AW34" r:id="rId240" tooltip="https://www.amazon.it/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A2WUCJY3ZYROH"/>
+    <hyperlink ref="C35" r:id="rId241" tooltip="https://www.amazon.it/dp/B0GLNFSYRW"/>
+    <hyperlink ref="G35" r:id="rId242" tooltip="https://www.amazon.it/s/ref=bl_dp_s_web_0?ie=UTF8&amp;search-alias=aps&amp;field-keywords=Vozascly"/>
+    <hyperlink ref="J35" r:id="rId243" tooltip="https://www.amazon.it/dp/B0GLNFSYRW?psc=1"/>
+    <hyperlink ref="K35" r:id="rId244" tooltip="https://m.media-amazon.com/images/I/41zOwfkwiCL._AC_US600_.jpg"/>
+    <hyperlink ref="L35" r:id="rId245" tooltip="https://www.amazon.it/dp/B0GLNFSYRW"/>
+    <hyperlink ref="M35" r:id="rId246" tooltip="https://www.amazon.it/b?node=733005031"/>
+    <hyperlink ref="N35" r:id="rId247"/>
+    <hyperlink ref="AW35" r:id="rId248" tooltip="https://www.amazon.it/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=AEBC603LGC1S2"/>
+    <hyperlink ref="C36" r:id="rId249" tooltip="https://www.amazon.it/dp/B0BSHCQQ4W"/>
+    <hyperlink ref="G36" r:id="rId250" tooltip="https://www.amazon.it/stores/HKoenig/page/978AEC1C-8AF0-4DD0-AECD-D6014C0418DD?lp_asin=B0BSHCQQ4W&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto&amp;bl_grd_status=override"/>
+    <hyperlink ref="J36" r:id="rId251" tooltip="https://www.amazon.it/dp/B0BSHCQQ4W?psc=1"/>
+    <hyperlink ref="K36" r:id="rId252" tooltip="https://m.media-amazon.com/images/I/41EDgJP8-JL._AC_US600_.jpg"/>
+    <hyperlink ref="L36" r:id="rId253" tooltip="https://www.amazon.it/dp/B0BSHCQQ4W"/>
+    <hyperlink ref="M36" r:id="rId254" tooltip="https://www.amazon.it/b?node=733005031"/>
+    <hyperlink ref="N36" r:id="rId255"/>
+    <hyperlink ref="AW36" r:id="rId256" tooltip="https://www.amazon.it/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A2J1ZXSJG29176"/>
+    <hyperlink ref="C37" r:id="rId257" tooltip="https://www.amazon.it/dp/B0FJFDG5PY"/>
+    <hyperlink ref="G37" r:id="rId258" tooltip="https://www.amazon.it/stores/Akitas/page/EE82F545-EF96-443C-8B75-30C504BE3C43?lp_asin=B0FJFDG5PY&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto&amp;bl_grd_status=override"/>
+    <hyperlink ref="J37" r:id="rId259" tooltip="https://www.amazon.it/dp/B0FJFDG5PY?psc=1"/>
+    <hyperlink ref="K37" r:id="rId260" tooltip="https://m.media-amazon.com/images/I/41MJX3SSe4L._AC_US600_.jpg"/>
+    <hyperlink ref="L37" r:id="rId261" tooltip="https://www.amazon.it/dp/B0FJFDG5PY"/>
+    <hyperlink ref="M37" r:id="rId262" tooltip="https://www.amazon.it/b?node=733005031"/>
+    <hyperlink ref="N37" r:id="rId263"/>
+    <hyperlink ref="AW37" r:id="rId264" tooltip="https://www.amazon.it/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A3ZOAHYWM588P"/>
+    <hyperlink ref="C38" r:id="rId265" tooltip="https://www.amazon.it/dp/B0BTHFNNH1"/>
+    <hyperlink ref="G38" r:id="rId266" tooltip="https://www.amazon.it/stores/VACMASTER/page/F372FF16-5498-423D-9923-A4EFB43DC86B?lp_asin=B0BTHFNNH1&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto"/>
+    <hyperlink ref="J38" r:id="rId267" tooltip="https://www.amazon.it/dp/B0BTHFNNH1?psc=1"/>
+    <hyperlink ref="K38" r:id="rId268" tooltip="https://images-na.ssl-images-amazon.com/images/I/81ygbNkGjPL._AC_US600_.jpg"/>
+    <hyperlink ref="L38" r:id="rId269" tooltip="https://www.amazon.it/dp/B0BTHFNNH1"/>
+    <hyperlink ref="M38" r:id="rId270" tooltip="https://www.amazon.it/b?node=733005031"/>
+    <hyperlink ref="N38" r:id="rId271"/>
+    <hyperlink ref="C39" r:id="rId272" tooltip="https://www.amazon.it/dp/B0D2HFLM1C"/>
+    <hyperlink ref="G39" r:id="rId273" tooltip="https://www.amazon.it/stores/HAUSHOF/page/9EE9CFD0-E18C-46CA-98BB-FA1050DF3283?lp_asin=B0D2HFLM1C&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto"/>
+    <hyperlink ref="J39" r:id="rId274" tooltip="https://www.amazon.it/dp/B0D2HFLM1C?psc=1"/>
+    <hyperlink ref="K39" r:id="rId275" tooltip="https://images-na.ssl-images-amazon.com/images/I/71cgtv2WdbL._AC_US600_.jpg"/>
+    <hyperlink ref="L39" r:id="rId276" tooltip="https://www.amazon.it/dp/B0D2HFLM1C"/>
     <hyperlink ref="M39" r:id="rId277" tooltip="https://www.amazon.it/b?node=733005031"/>
     <hyperlink ref="N39" r:id="rId278"/>
-    <hyperlink ref="C40" r:id="rId279" tooltip="https://www.amazon.it/dp/B0D2HFLM1C"/>
-    <hyperlink ref="G40" r:id="rId280" tooltip="https://www.amazon.it/stores/HAUSHOF/page/9EE9CFD0-E18C-46CA-98BB-FA1050DF3283?lp_asin=B0D2HFLM1C&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto"/>
-    <hyperlink ref="J40" r:id="rId281" tooltip="https://www.amazon.it/dp/B0D2HFLM1C?psc=1"/>
-    <hyperlink ref="K40" r:id="rId282" tooltip="https://images-na.ssl-images-amazon.com/images/I/71cgtv2WdbL._AC_US600_.jpg"/>
-    <hyperlink ref="L40" r:id="rId283" tooltip="https://www.amazon.it/dp/B0D2HFLM1C"/>
+    <hyperlink ref="C40" r:id="rId279" tooltip="https://www.amazon.it/dp/B0FHB8RB8F"/>
+    <hyperlink ref="G40" r:id="rId280" tooltip="https://www.amazon.it/Cecotec/b/ref=bl_dp_s_web_19986335031?ie=UTF8&amp;node=19986335031&amp;field-lbr_brands_browse-bin=Cecotec"/>
+    <hyperlink ref="J40" r:id="rId281" tooltip="https://www.amazon.it/dp/B0FHB8RB8F?psc=1"/>
+    <hyperlink ref="K40" r:id="rId282" tooltip="https://m.media-amazon.com/images/I/411-YObj2pL._AC_US600_.jpg"/>
+    <hyperlink ref="L40" r:id="rId283" tooltip="https://www.amazon.it/dp/B0FHB8RB8F"/>
     <hyperlink ref="M40" r:id="rId284" tooltip="https://www.amazon.it/b?node=733005031"/>
     <hyperlink ref="N40" r:id="rId285"/>
-    <hyperlink ref="C41" r:id="rId286" tooltip="https://www.amazon.it/dp/B0FHB8RB8F"/>
-    <hyperlink ref="G41" r:id="rId287" tooltip="https://www.amazon.it/Cecotec/b/ref=bl_dp_s_web_19986335031?ie=UTF8&amp;node=19986335031&amp;field-lbr_brands_browse-bin=Cecotec"/>
-    <hyperlink ref="J41" r:id="rId288" tooltip="https://www.amazon.it/dp/B0FHB8RB8F?psc=1"/>
-    <hyperlink ref="K41" r:id="rId289" tooltip="https://m.media-amazon.com/images/I/411-YObj2pL._AC_US600_.jpg"/>
-    <hyperlink ref="L41" r:id="rId290" tooltip="https://www.amazon.it/dp/B0FHB8RB8F"/>
+    <hyperlink ref="C41" r:id="rId286" tooltip="https://www.amazon.it/dp/B0CLYF3DMZ"/>
+    <hyperlink ref="G41" r:id="rId287" tooltip="https://www.amazon.it/stores/LEHMANN/page/F8312757-EA08-4E70-8102-256521882264?lp_asin=B0CLYF3DMZ&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto&amp;bl_grd_status=override"/>
+    <hyperlink ref="J41" r:id="rId288" tooltip="https://www.amazon.it/dp/B0CLYF3DMZ?psc=1"/>
+    <hyperlink ref="K41" r:id="rId289" tooltip="https://m.media-amazon.com/images/I/41IUxMxofsL._AC_US600_.jpg"/>
+    <hyperlink ref="L41" r:id="rId290" tooltip="https://www.amazon.it/dp/B0CLYF3DMZ"/>
     <hyperlink ref="M41" r:id="rId291" tooltip="https://www.amazon.it/b?node=733005031"/>
     <hyperlink ref="N41" r:id="rId292"/>
-    <hyperlink ref="C42" r:id="rId293" tooltip="https://www.amazon.it/dp/B0CLYF3DMZ"/>
-    <hyperlink ref="G42" r:id="rId294" tooltip="https://www.amazon.it/stores/LEHMANN/page/F8312757-EA08-4E70-8102-256521882264?lp_asin=B0CLYF3DMZ&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto&amp;bl_grd_status=override"/>
-    <hyperlink ref="J42" r:id="rId295" tooltip="https://www.amazon.it/dp/B0CLYF3DMZ?psc=1"/>
-    <hyperlink ref="K42" r:id="rId296" tooltip="https://m.media-amazon.com/images/I/41IUxMxofsL._AC_US600_.jpg"/>
-    <hyperlink ref="L42" r:id="rId297" tooltip="https://www.amazon.it/dp/B0CLYF3DMZ"/>
-    <hyperlink ref="M42" r:id="rId298" tooltip="https://www.amazon.it/b?node=733005031"/>
-    <hyperlink ref="N42" r:id="rId299"/>
-    <hyperlink ref="AW42" r:id="rId300" tooltip="https://www.amazon.it/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A2WUCJY3ZYROH"/>
-    <hyperlink ref="C43" r:id="rId301" tooltip="https://www.amazon.it/dp/B0GH6TBJVW"/>
-    <hyperlink ref="G43" r:id="rId302" tooltip="https://www.amazon.it/s/ref=bl_dp_s_web_0?ie=UTF8&amp;search-alias=aps&amp;field-keywords=Kitcanis"/>
-    <hyperlink ref="J43" r:id="rId303" tooltip="https://www.amazon.it/dp/B0GH6TBJVW?psc=1"/>
-    <hyperlink ref="K43" r:id="rId304" tooltip="https://m.media-amazon.com/images/I/51LdyRohTNL._AC_US600_.jpg"/>
-    <hyperlink ref="L43" r:id="rId305" tooltip="https://www.amazon.it/dp/B0GH6TBJVW"/>
-    <hyperlink ref="M43" r:id="rId306" tooltip="https://www.amazon.it/b?node=733005031"/>
-    <hyperlink ref="N43" r:id="rId307"/>
-    <hyperlink ref="AW43" r:id="rId308" tooltip="https://www.amazon.it/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A3SC5MLKO5B7LX"/>
-    <hyperlink ref="C44" r:id="rId309" tooltip="https://www.amazon.it/dp/B0BPZJSXCQ"/>
-    <hyperlink ref="G44" r:id="rId310" tooltip="https://www.amazon.it/Cecotec/b/ref=bl_dp_s_web_19986335031?ie=UTF8&amp;node=19986335031&amp;field-lbr_brands_browse-bin=Cecotec"/>
-    <hyperlink ref="J44" r:id="rId311" tooltip="https://www.amazon.it/dp/B0BPZJSXCQ?psc=1"/>
-    <hyperlink ref="K44" r:id="rId312" tooltip="https://m.media-amazon.com/images/I/41-V4acAJLL._AC_US600_.jpg"/>
-    <hyperlink ref="L44" r:id="rId313" tooltip="https://www.amazon.it/dp/B0BPZJSXCQ"/>
-    <hyperlink ref="M44" r:id="rId314" tooltip="https://www.amazon.it/b?node=733005031"/>
-    <hyperlink ref="N44" r:id="rId315"/>
-    <hyperlink ref="AW44" r:id="rId316" tooltip="https://www.amazon.it/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A1PTIZUJDIGRO9"/>
-    <hyperlink ref="C45" r:id="rId317" tooltip="https://www.amazon.it/dp/B0CM6TD52F"/>
-    <hyperlink ref="G45" r:id="rId318" tooltip="https://www.amazon.it/stores/LEHMANN/page/F8312757-EA08-4E70-8102-256521882264?lp_asin=B0CM6TD52F&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto&amp;bl_grd_status=override"/>
-    <hyperlink ref="J45" r:id="rId319" tooltip="https://www.amazon.it/dp/B0CM6TD52F?psc=1"/>
-    <hyperlink ref="K45" r:id="rId320" tooltip="https://m.media-amazon.com/images/I/41zsYT7ETXL._AC_US600_.jpg"/>
-    <hyperlink ref="L45" r:id="rId321" tooltip="https://www.amazon.it/dp/B0CM6TD52F"/>
-    <hyperlink ref="M45" r:id="rId322" tooltip="https://www.amazon.it/b?node=733005031"/>
-    <hyperlink ref="N45" r:id="rId323"/>
-    <hyperlink ref="AW45" r:id="rId324" tooltip="https://www.amazon.it/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A2WUCJY3ZYROH"/>
-    <hyperlink ref="C46" r:id="rId325" tooltip="https://www.amazon.it/dp/B0GFF7C519"/>
-    <hyperlink ref="G46" r:id="rId326" tooltip="https://www.amazon.it/stores/Akitas/page/EE82F545-EF96-443C-8B75-30C504BE3C43?lp_asin=B0GFF7C519&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto&amp;bl_grd_status=override"/>
-    <hyperlink ref="J46" r:id="rId327" tooltip="https://www.amazon.it/dp/B0GFF7C519?psc=1"/>
-    <hyperlink ref="K46" r:id="rId328" tooltip="https://m.media-amazon.com/images/I/41qPnZFK2xL._AC_US600_.jpg"/>
-    <hyperlink ref="L46" r:id="rId329" tooltip="https://www.amazon.it/dp/B0GFF7C519"/>
-    <hyperlink ref="M46" r:id="rId330" tooltip="https://www.amazon.it/b?node=733005031"/>
-    <hyperlink ref="N46" r:id="rId331"/>
-    <hyperlink ref="AW46" r:id="rId332" tooltip="https://www.amazon.it/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A3ZOAHYWM588P"/>
-    <hyperlink ref="C47" r:id="rId333" tooltip="https://www.amazon.it/dp/B086Q46MMD"/>
-    <hyperlink ref="G47" r:id="rId334" tooltip="https://www.amazon.it/stores/STANHOME/page/CF140807-E9D9-4EE4-98E8-28F83571D17F?lp_asin=B086Q46MMD&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto&amp;bl_grd_status=override"/>
-    <hyperlink ref="J47" r:id="rId335" tooltip="https://www.amazon.it/dp/B086Q46MMD?psc=1"/>
-    <hyperlink ref="K47" r:id="rId336" tooltip="https://m.media-amazon.com/images/I/31hUTFxCzpL._AC_US600_.jpg"/>
-    <hyperlink ref="L47" r:id="rId337" tooltip="https://www.amazon.it/dp/B086Q46MMD"/>
-    <hyperlink ref="M47" r:id="rId338" tooltip="https://www.amazon.it/b?node=733005031"/>
-    <hyperlink ref="N47" r:id="rId339"/>
-    <hyperlink ref="AW47" r:id="rId340" tooltip="https://www.amazon.it/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A1FKDALFGWQLQF"/>
-    <hyperlink ref="C48" r:id="rId341" tooltip="https://www.amazon.it/dp/B0H3KVMBCH"/>
-    <hyperlink ref="G48" r:id="rId342" tooltip="https://www.amazon.it/s/ref=bl_dp_s_web_0?ie=UTF8&amp;search-alias=aps&amp;field-keywords=MELLWIN"/>
-    <hyperlink ref="J48" r:id="rId343" tooltip="https://www.amazon.it/dp/B0H3KVMBCH?psc=1"/>
-    <hyperlink ref="K48" r:id="rId344" tooltip="https://m.media-amazon.com/images/I/41W3WF+EhbL._AC_US600_.jpg"/>
-    <hyperlink ref="L48" r:id="rId345" tooltip="https://www.amazon.it/dp/B0H3KVMBCH"/>
+    <hyperlink ref="AW41" r:id="rId293" tooltip="https://www.amazon.it/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A2WUCJY3ZYROH"/>
+    <hyperlink ref="C42" r:id="rId294" tooltip="https://www.amazon.it/dp/B0GH6TBJVW"/>
+    <hyperlink ref="G42" r:id="rId295" tooltip="https://www.amazon.it/s/ref=bl_dp_s_web_0?ie=UTF8&amp;search-alias=aps&amp;field-keywords=Kitcanis"/>
+    <hyperlink ref="J42" r:id="rId296" tooltip="https://www.amazon.it/dp/B0GH6TBJVW?psc=1"/>
+    <hyperlink ref="K42" r:id="rId297" tooltip="https://m.media-amazon.com/images/I/51LdyRohTNL._AC_US600_.jpg"/>
+    <hyperlink ref="L42" r:id="rId298" tooltip="https://www.amazon.it/dp/B0GH6TBJVW"/>
+    <hyperlink ref="M42" r:id="rId299" tooltip="https://www.amazon.it/b?node=733005031"/>
+    <hyperlink ref="N42" r:id="rId300"/>
+    <hyperlink ref="AW42" r:id="rId301" tooltip="https://www.amazon.it/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A3SC5MLKO5B7LX"/>
+    <hyperlink ref="C43" r:id="rId302" tooltip="https://www.amazon.it/dp/B0BPZJSXCQ"/>
+    <hyperlink ref="G43" r:id="rId303" tooltip="https://www.amazon.it/Cecotec/b/ref=bl_dp_s_web_19986335031?ie=UTF8&amp;node=19986335031&amp;field-lbr_brands_browse-bin=Cecotec"/>
+    <hyperlink ref="J43" r:id="rId304" tooltip="https://www.amazon.it/dp/B0BPZJSXCQ?psc=1"/>
+    <hyperlink ref="K43" r:id="rId305" tooltip="https://m.media-amazon.com/images/I/41-V4acAJLL._AC_US600_.jpg"/>
+    <hyperlink ref="L43" r:id="rId306" tooltip="https://www.amazon.it/dp/B0BPZJSXCQ"/>
+    <hyperlink ref="M43" r:id="rId307" tooltip="https://www.amazon.it/b?node=733005031"/>
+    <hyperlink ref="N43" r:id="rId308"/>
+    <hyperlink ref="AW43" r:id="rId309" tooltip="https://www.amazon.it/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A1PTIZUJDIGRO9"/>
+    <hyperlink ref="C44" r:id="rId310" tooltip="https://www.amazon.it/dp/B0CM6TD52F"/>
+    <hyperlink ref="G44" r:id="rId311" tooltip="https://www.amazon.it/stores/LEHMANN/page/F8312757-EA08-4E70-8102-256521882264?lp_asin=B0CM6TD52F&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto&amp;bl_grd_status=override"/>
+    <hyperlink ref="J44" r:id="rId312" tooltip="https://www.amazon.it/dp/B0CM6TD52F?psc=1"/>
+    <hyperlink ref="K44" r:id="rId313" tooltip="https://m.media-amazon.com/images/I/41zsYT7ETXL._AC_US600_.jpg"/>
+    <hyperlink ref="L44" r:id="rId314" tooltip="https://www.amazon.it/dp/B0CM6TD52F"/>
+    <hyperlink ref="M44" r:id="rId315" tooltip="https://www.amazon.it/b?node=733005031"/>
+    <hyperlink ref="N44" r:id="rId316"/>
+    <hyperlink ref="AW44" r:id="rId317" tooltip="https://www.amazon.it/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A2WUCJY3ZYROH"/>
+    <hyperlink ref="C45" r:id="rId318" tooltip="https://www.amazon.it/dp/B0GFF7C519"/>
+    <hyperlink ref="G45" r:id="rId319" tooltip="https://www.amazon.it/stores/Akitas/page/EE82F545-EF96-443C-8B75-30C504BE3C43?lp_asin=B0GFF7C519&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto&amp;bl_grd_status=override"/>
+    <hyperlink ref="J45" r:id="rId320" tooltip="https://www.amazon.it/dp/B0GFF7C519?psc=1"/>
+    <hyperlink ref="K45" r:id="rId321" tooltip="https://m.media-amazon.com/images/I/41qPnZFK2xL._AC_US600_.jpg"/>
+    <hyperlink ref="L45" r:id="rId322" tooltip="https://www.amazon.it/dp/B0GFF7C519"/>
+    <hyperlink ref="M45" r:id="rId323" tooltip="https://www.amazon.it/b?node=733005031"/>
+    <hyperlink ref="N45" r:id="rId324"/>
+    <hyperlink ref="AW45" r:id="rId325" tooltip="https://www.amazon.it/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A3ZOAHYWM588P"/>
+    <hyperlink ref="C46" r:id="rId326" tooltip="https://www.amazon.it/dp/B0H3KVMBCH"/>
+    <hyperlink ref="G46" r:id="rId327" tooltip="https://www.amazon.it/s/ref=bl_dp_s_web_0?ie=UTF8&amp;search-alias=aps&amp;field-keywords=MELLWIN"/>
+    <hyperlink ref="J46" r:id="rId328" tooltip="https://www.amazon.it/dp/B0H3KVMBCH?psc=1"/>
+    <hyperlink ref="K46" r:id="rId329" tooltip="https://m.media-amazon.com/images/I/41W3WF+EhbL._AC_US600_.jpg"/>
+    <hyperlink ref="L46" r:id="rId330" tooltip="https://www.amazon.it/dp/B0H3KVMBCH"/>
+    <hyperlink ref="M46" r:id="rId331" tooltip="https://www.amazon.it/b?node=733005031"/>
+    <hyperlink ref="N46" r:id="rId332"/>
+    <hyperlink ref="AW46" r:id="rId333" tooltip="https://www.amazon.it/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=ABSTVEQNNON26"/>
+    <hyperlink ref="C47" r:id="rId334" tooltip="https://www.amazon.it/dp/B0H4TXR27S"/>
+    <hyperlink ref="G47" r:id="rId335" tooltip="https://www.amazon.it/stores/Redkey/page/D0F8E94D-480F-4BD7-ADC2-FEE4358EEB34?lp_asin=B0H4TXR27S&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto"/>
+    <hyperlink ref="J47" r:id="rId336" tooltip="https://www.amazon.it/dp/B0H4TXR27S?psc=1"/>
+    <hyperlink ref="K47" r:id="rId337" tooltip="https://m.media-amazon.com/images/I/41f8wwTeaGL._AC_US600_.jpg"/>
+    <hyperlink ref="L47" r:id="rId338" tooltip="https://www.amazon.it/dp/B0H4TXR27S"/>
+    <hyperlink ref="M47" r:id="rId339" tooltip="https://www.amazon.it/b?node=733005031"/>
+    <hyperlink ref="N47" r:id="rId340"/>
+    <hyperlink ref="C48" r:id="rId341" tooltip="https://www.amazon.it/dp/B0H97LW9DL"/>
+    <hyperlink ref="G48" r:id="rId342" tooltip="https://www.amazon.it/stores/Rispostaimmediatain24ore/page/DC11DA78-3928-4F1D-8E2F-8AD84D6FF0A2?lp_asin=B0H97LW9DL&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto&amp;bl_grd_status=override"/>
+    <hyperlink ref="J48" r:id="rId343" tooltip="https://www.amazon.it/dp/B0H97LW9DL?psc=1"/>
+    <hyperlink ref="K48" r:id="rId344" tooltip="https://images-na.ssl-images-amazon.com/images/I/51LnggCx6eL._AC_US600_.jpg"/>
+    <hyperlink ref="L48" r:id="rId345" tooltip="https://www.amazon.it/dp/B0H97LW9DL"/>
     <hyperlink ref="M48" r:id="rId346" tooltip="https://www.amazon.it/b?node=733005031"/>
     <hyperlink ref="N48" r:id="rId347"/>
-    <hyperlink ref="AW48" r:id="rId348" tooltip="https://www.amazon.it/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=ABSTVEQNNON26"/>
-    <hyperlink ref="C49" r:id="rId349" tooltip="https://www.amazon.it/dp/B0H4TXR27S"/>
-    <hyperlink ref="G49" r:id="rId350" tooltip="https://www.amazon.it/stores/Redkey/page/D0F8E94D-480F-4BD7-ADC2-FEE4358EEB34?lp_asin=B0H4TXR27S&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto"/>
-    <hyperlink ref="J49" r:id="rId351" tooltip="https://www.amazon.it/dp/B0H4TXR27S?psc=1"/>
-    <hyperlink ref="K49" r:id="rId352" tooltip="https://m.media-amazon.com/images/I/41f8wwTeaGL._AC_US600_.jpg"/>
-    <hyperlink ref="L49" r:id="rId353" tooltip="https://www.amazon.it/dp/B0H4TXR27S"/>
-    <hyperlink ref="M49" r:id="rId354" tooltip="https://www.amazon.it/b?node=733005031"/>
-    <hyperlink ref="N49" r:id="rId355"/>
-    <hyperlink ref="C50" r:id="rId356" tooltip="https://www.amazon.it/dp/B0H97LW9DL"/>
-    <hyperlink ref="G50" r:id="rId357" tooltip="https://www.amazon.it/stores/Rispostaimmediatain24ore/page/DC11DA78-3928-4F1D-8E2F-8AD84D6FF0A2?lp_asin=B0H97LW9DL&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto&amp;bl_grd_status=override"/>
-    <hyperlink ref="J50" r:id="rId358" tooltip="https://www.amazon.it/dp/B0H97LW9DL?psc=1"/>
-    <hyperlink ref="K50" r:id="rId359" tooltip="https://images-na.ssl-images-amazon.com/images/I/51LnggCx6eL._AC_US600_.jpg"/>
-    <hyperlink ref="L50" r:id="rId360" tooltip="https://www.amazon.it/dp/B0H97LW9DL"/>
-    <hyperlink ref="M50" r:id="rId361" tooltip="https://www.amazon.it/b?node=733005031"/>
-    <hyperlink ref="N50" r:id="rId362"/>
-    <hyperlink ref="AW50" r:id="rId363" tooltip="https://www.amazon.it/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A1SGZEKAW8X162"/>
-    <hyperlink ref="C51" r:id="rId364" tooltip="https://www.amazon.it/dp/B08KXVXC82"/>
-    <hyperlink ref="G51" r:id="rId365" tooltip="https://www.amazon.itundefined"/>
-    <hyperlink ref="J51" r:id="rId366" tooltip="https://www.amazon.it/dp/B08KXVXC82?psc=1"/>
-    <hyperlink ref="K51" r:id="rId367" tooltip="https://images-eu.ssl-images-amazon.com/images/I/71A5BQeECwL._AC_UL300_SR300,200_.jpg"/>
-    <hyperlink ref="L51" r:id="rId368" tooltip="https://www.amazon.it/dp/B08KXVXC82"/>
+    <hyperlink ref="AW48" r:id="rId348" tooltip="https://www.amazon.it/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A1SGZEKAW8X162"/>
+    <hyperlink ref="C49" r:id="rId349" tooltip="https://www.amazon.it/dp/B08KXVXC82"/>
+    <hyperlink ref="G49" r:id="rId350" tooltip="https://www.amazon.itundefined"/>
+    <hyperlink ref="J49" r:id="rId351" tooltip="https://www.amazon.it/dp/B08KXVXC82?psc=1"/>
+    <hyperlink ref="K49" r:id="rId352" tooltip="https://images-eu.ssl-images-amazon.com/images/I/71A5BQeECwL._AC_UL300_SR300,200_.jpg"/>
+    <hyperlink ref="L49" r:id="rId353" tooltip="https://www.amazon.it/dp/B08KXVXC82"/>
   </hyperlinks>
-  <drawing r:id="rId369"/>
+  <drawing r:id="rId354"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:G26"/>
+  <dimension ref="A1:G25"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="25" style="1" customWidth="1"/>
@@ -19224,18 +18663,18 @@
         </is>
       </c>
       <c r="B2" s="15">
-        <v>6852</v>
+        <v>6068</v>
       </c>
       <c r="C2" s="15">
-        <v>730121</v>
+        <v>718369</v>
       </c>
       <c r="D2" s="15"/>
       <c r="E2" s="15"/>
       <c r="F2" s="20">
-        <v>106.55589608873322</v>
+        <v>118.38645352669742</v>
       </c>
       <c r="G2" s="22">
-        <v>0.44496395869861677</v>
+        <v>0.41839619389091914</v>
       </c>
     </row>
     <row r="3" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -19256,7 +18695,7 @@
         <v>147.17857142857142</v>
       </c>
       <c r="G3" s="22">
-        <v>0.05636729657769985</v>
+        <v>0.059849686271805834</v>
       </c>
     </row>
     <row r="4" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -19277,7 +18716,7 @@
         <v>92.42402315484804</v>
       </c>
       <c r="G4" s="22">
-        <v>0.08974608740827326</v>
+        <v>0.09529062952492588</v>
       </c>
     </row>
     <row r="5" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -19298,7 +18737,7 @@
         <v>79.98996655518394</v>
       </c>
       <c r="G5" s="22">
-        <v>0.0970842262484577</v>
+        <v>0.10308212094049507</v>
       </c>
     </row>
     <row r="6" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -19319,7 +18758,7 @@
         <v>220.3049645390071</v>
       </c>
       <c r="G6" s="22">
-        <v>0.018312877459575296</v>
+        <v>0.019444252913190373</v>
       </c>
     </row>
     <row r="7" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -19340,7 +18779,7 @@
         <v>68.38965952080706</v>
       </c>
       <c r="G7" s="22">
-        <v>0.05149685044483408</v>
+        <v>0.05467834241191478</v>
       </c>
     </row>
     <row r="8" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -19361,7 +18800,7 @@
         <v>160.03010033444815</v>
       </c>
       <c r="G8" s="22">
-        <v>0.019416845249691537</v>
+        <v>0.020616424188099013</v>
       </c>
     </row>
     <row r="9" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -19382,7 +18821,7 @@
         <v>125.80938416422288</v>
       </c>
       <c r="G9" s="22">
-        <v>0.02214429508409637</v>
+        <v>0.023512376749638006</v>
       </c>
     </row>
     <row r="10" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -19403,7 +18842,7 @@
         <v>95.19545454545455</v>
       </c>
       <c r="G10" s="22">
-        <v>0.028573283979479187</v>
+        <v>0.0303385506446942</v>
       </c>
     </row>
     <row r="11" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -19424,7 +18863,7 @@
         <v>95.07194244604317</v>
       </c>
       <c r="G11" s="22">
-        <v>0.027079680498733685</v>
+        <v>0.028752671860994276</v>
       </c>
     </row>
     <row r="12" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -19445,7 +18884,7 @@
         <v>149.992</v>
       </c>
       <c r="G12" s="22">
-        <v>0.016234820442885902</v>
+        <v>0.017237812866303524</v>
       </c>
     </row>
     <row r="13" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -19466,7 +18905,7 @@
         <v>74.0</v>
       </c>
       <c r="G13" s="22">
-        <v>0.02792389116176375</v>
+        <v>0.02964903813004206</v>
       </c>
     </row>
     <row r="14" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -19487,7 +18926,7 @@
         <v>179.99193548387098</v>
       </c>
       <c r="G14" s="22">
-        <v>0.008052470939671407</v>
+        <v>0.008549955181686547</v>
       </c>
     </row>
     <row r="15" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -19508,7 +18947,7 @@
         <v>96.38073394495413</v>
       </c>
       <c r="G15" s="22">
-        <v>0.014156763426196506</v>
+        <v>0.015031372819416673</v>
       </c>
     </row>
     <row r="16" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -19529,7 +18968,7 @@
         <v>179.98850574712642</v>
       </c>
       <c r="G16" s="22">
-        <v>0.005649717514124294</v>
+        <v>0.005998758877473626</v>
       </c>
     </row>
     <row r="17" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -19550,7 +18989,7 @@
         <v>69.99103139013452</v>
       </c>
       <c r="G17" s="22">
-        <v>0.014481459835054224</v>
+        <v>0.015376129076742743</v>
       </c>
     </row>
     <row r="18" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -19571,7 +19010,7 @@
         <v>74.38378378378378</v>
       </c>
       <c r="G18" s="22">
-        <v>0.012013767127735567</v>
+        <v>0.012755981521064608</v>
       </c>
     </row>
     <row r="19" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -19592,7 +19031,7 @@
         <v>80.90066225165563</v>
       </c>
       <c r="G19" s="22">
-        <v>0.009805831547503084</v>
+        <v>0.010411638971247328</v>
       </c>
     </row>
     <row r="20" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -19613,7 +19052,7 @@
         <v>119.9888888888889</v>
       </c>
       <c r="G20" s="22">
-        <v>0.0058445353594389245</v>
+        <v>0.006205612631869269</v>
       </c>
     </row>
     <row r="21" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -19634,7 +19073,7 @@
         <v>107.68</v>
       </c>
       <c r="G21" s="22">
-        <v>0.006493928177154361</v>
+        <v>0.006895125146521409</v>
       </c>
     </row>
     <row r="22" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -19655,7 +19094,7 @@
         <v>59.899441340782126</v>
       </c>
       <c r="G22" s="22">
-        <v>0.011624131437106305</v>
+        <v>0.012342274012273323</v>
       </c>
     </row>
     <row r="23" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -19676,67 +19115,46 @@
         <v>74.49253731343283</v>
       </c>
       <c r="G23" s="22">
-        <v>0.0043509318786934216</v>
+        <v>0.004619733848169345</v>
       </c>
     </row>
     <row r="24" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="14" t="inlineStr">
         <is>
-          <t>STANHOME</t>
+          <t>MELLWIN</t>
         </is>
       </c>
       <c r="B24" s="15">
-        <v>112</v>
+        <v>14</v>
       </c>
       <c r="C24" s="15">
-        <v>1680</v>
+        <v>1452</v>
       </c>
       <c r="D24" s="15"/>
       <c r="E24" s="15"/>
       <c r="F24" s="20">
-        <v>15.0</v>
+        <v>103.71428571428571</v>
       </c>
       <c r="G24" s="22">
-        <v>0.007273199558412884</v>
+        <v>0.0009653175205129973</v>
       </c>
     </row>
     <row r="25" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" s="14" t="inlineStr">
         <is>
-          <t>MELLWIN</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="B25" s="15">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="C25" s="15">
-        <v>1452</v>
+        <v>0</v>
       </c>
       <c r="D25" s="15"/>
       <c r="E25" s="15"/>
-      <c r="F25" s="20">
-        <v>103.71428571428571</v>
-      </c>
+      <c r="F25" s="20"/>
       <c r="G25" s="22">
-        <v>0.0009091499448016105</v>
-      </c>
-    </row>
-    <row r="26" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A26" s="14" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="B26" s="15">
-        <v>0</v>
-      </c>
-      <c r="C26" s="15">
-        <v>0</v>
-      </c>
-      <c r="D26" s="15"/>
-      <c r="E26" s="15"/>
-      <c r="F26" s="20"/>
-      <c r="G26" s="22">
         <v>0.0</v>
       </c>
     </row>
@@ -19748,7 +19166,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:G18"/>
+  <dimension ref="A1:G17"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="25" style="1" customWidth="1"/>
@@ -19801,18 +19219,18 @@
         </is>
       </c>
       <c r="B2" s="15">
-        <v>10852</v>
+        <v>10068</v>
       </c>
       <c r="C2" s="15">
-        <v>1207487</v>
+        <v>1195735</v>
       </c>
       <c r="D2" s="15"/>
       <c r="E2" s="15"/>
       <c r="F2" s="20">
-        <v>111.26861408035386</v>
+        <v>118.76589193484307</v>
       </c>
       <c r="G2" s="22">
-        <v>0.7047210857847912</v>
+        <v>0.6942011997517755</v>
       </c>
     </row>
     <row r="3" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -19833,7 +19251,7 @@
         <v>79.98996655518394</v>
       </c>
       <c r="G3" s="22">
-        <v>0.0970842262484577</v>
+        <v>0.10308212094049507</v>
       </c>
     </row>
     <row r="4" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -19854,7 +19272,7 @@
         <v>68.38965952080706</v>
       </c>
       <c r="G4" s="22">
-        <v>0.05149685044483408</v>
+        <v>0.05467834241191478</v>
       </c>
     </row>
     <row r="5" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -19875,7 +19293,7 @@
         <v>95.19545454545455</v>
       </c>
       <c r="G5" s="22">
-        <v>0.028573283979479187</v>
+        <v>0.0303385506446942</v>
       </c>
     </row>
     <row r="6" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -19896,7 +19314,7 @@
         <v>149.992</v>
       </c>
       <c r="G6" s="22">
-        <v>0.016234820442885902</v>
+        <v>0.017237812866303524</v>
       </c>
     </row>
     <row r="7" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -19917,7 +19335,7 @@
         <v>83.03628117913833</v>
       </c>
       <c r="G7" s="22">
-        <v>0.02863822326125073</v>
+        <v>0.030407501896159414</v>
       </c>
     </row>
     <row r="8" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -19938,7 +19356,7 @@
         <v>151.98984771573603</v>
       </c>
       <c r="G8" s="22">
-        <v>0.012793038508994091</v>
+        <v>0.013583396538647177</v>
       </c>
     </row>
     <row r="9" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -19959,7 +19377,7 @@
         <v>179.98888888888888</v>
       </c>
       <c r="G9" s="22">
-        <v>0.0058445353594389245</v>
+        <v>0.006205612631869269</v>
       </c>
     </row>
     <row r="10" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -19980,7 +19398,7 @@
         <v>74.38378378378378</v>
       </c>
       <c r="G10" s="22">
-        <v>0.012013767127735567</v>
+        <v>0.012755981521064608</v>
       </c>
     </row>
     <row r="11" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -20001,7 +19419,7 @@
         <v>89.99305555555556</v>
       </c>
       <c r="G11" s="22">
-        <v>0.009351256575102279</v>
+        <v>0.00992898021099083</v>
       </c>
     </row>
     <row r="12" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -20022,7 +19440,7 @@
         <v>119.9888888888889</v>
       </c>
       <c r="G12" s="22">
-        <v>0.0058445353594389245</v>
+        <v>0.006205612631869269</v>
       </c>
     </row>
     <row r="13" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -20043,7 +19461,7 @@
         <v>59.899441340782126</v>
       </c>
       <c r="G13" s="22">
-        <v>0.011624131437106305</v>
+        <v>0.012342274012273323</v>
       </c>
     </row>
     <row r="14" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -20064,7 +19482,7 @@
         <v>74.49253731343283</v>
       </c>
       <c r="G14" s="22">
-        <v>0.0043509318786934216</v>
+        <v>0.004619733848169345</v>
       </c>
     </row>
     <row r="15" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -20085,67 +19503,46 @@
         <v>86.36</v>
       </c>
       <c r="G15" s="22">
-        <v>0.0032469640885771805</v>
+        <v>0.0034475625732607045</v>
       </c>
     </row>
     <row r="16" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="14" t="inlineStr">
         <is>
-          <t>Stanhome S.p.A</t>
+          <t>EUROAPEX LANDING</t>
         </is>
       </c>
       <c r="B16" s="15">
-        <v>112</v>
+        <v>14</v>
       </c>
       <c r="C16" s="15">
-        <v>1680</v>
+        <v>1452</v>
       </c>
       <c r="D16" s="15"/>
       <c r="E16" s="15"/>
       <c r="F16" s="20">
-        <v>15.0</v>
+        <v>103.71428571428571</v>
       </c>
       <c r="G16" s="22">
-        <v>0.007273199558412884</v>
+        <v>0.0009653175205129973</v>
       </c>
     </row>
     <row r="17" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="14" t="inlineStr">
         <is>
-          <t>EUROAPEX LANDING</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="B17" s="15">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="C17" s="15">
-        <v>1452</v>
+        <v>0</v>
       </c>
       <c r="D17" s="15"/>
       <c r="E17" s="15"/>
-      <c r="F17" s="20">
-        <v>103.71428571428571</v>
-      </c>
+      <c r="F17" s="20"/>
       <c r="G17" s="22">
-        <v>0.0009091499448016105</v>
-      </c>
-    </row>
-    <row r="18" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A18" s="14" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="B18" s="15">
-        <v>0</v>
-      </c>
-      <c r="C18" s="15">
-        <v>0</v>
-      </c>
-      <c r="D18" s="15"/>
-      <c r="E18" s="15"/>
-      <c r="F18" s="20"/>
-      <c r="G18" s="22">
         <v>0.0</v>
       </c>
     </row>
